--- a/artfynd/A 2278-2026 artfynd.xlsx
+++ b/artfynd/A 2278-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,724 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134004110</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>a 2278-2026, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>594497</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7106185</v>
+      </c>
+      <c r="S3" t="n">
+        <v>8</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134004112</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>a 2278-2026, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>594779</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7106096</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134004114</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92235</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>658</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>a 2278-2026, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>594697</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7106106</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134004120</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58822</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>a 2278-2026, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>594671</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7106200</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134004119</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>a 2278-2026, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>594745</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7106148</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>osäker fynd</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134005846</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>594599</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7106170</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134004111</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>a 2278-2026, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>594815</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7106147</v>
+      </c>
+      <c r="S9" t="n">
+        <v>7</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2278-2026 artfynd.xlsx
+++ b/artfynd/A 2278-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134005846</v>
+        <v>134004111</v>
       </c>
       <c r="B8" t="n">
         <v>79334</v>
@@ -1338,17 +1338,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>a 2278-2026, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594599</v>
+        <v>594815</v>
       </c>
       <c r="R8" t="n">
-        <v>7106170</v>
+        <v>7106147</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1400,11 +1400,15 @@
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134004111</v>
+        <v>134005846</v>
       </c>
       <c r="B9" t="n">
         <v>79334</v>
@@ -1435,69 +1439,5688 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>a 2278-2026, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594815</v>
+        <v>594599</v>
       </c>
       <c r="R9" t="n">
-        <v>7106147</v>
+        <v>7106170</v>
       </c>
       <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134036167</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96366</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>594607</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7106088</v>
+      </c>
+      <c r="S10" t="n">
+        <v>30</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134040810</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80475</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>594501</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7106169</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134040804</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>594523</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7106019</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134040826</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96366</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>594724</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7106118</v>
+      </c>
+      <c r="S13" t="n">
+        <v>11</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134040803</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>594534</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7105996</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134040813</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>594504</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7106177</v>
+      </c>
+      <c r="S15" t="n">
         <v>7</v>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Västerbotten</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>Åsele lappmark</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134036149</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>594477</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7106037</v>
+      </c>
+      <c r="S16" t="n">
+        <v>16</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134041934</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91951</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Åsele Söndag Inventering, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>594559</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7106144</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134036160</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96366</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>594497</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7106164</v>
+      </c>
+      <c r="S18" t="n">
+        <v>32</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134036172</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80343</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>594619</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7106110</v>
+      </c>
+      <c r="S19" t="n">
+        <v>16</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134036159</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91951</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>594504</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7106148</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134040806</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91927</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>594500</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7106023</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134040808</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80475</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>594483</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7106035</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134036155</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80399</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>594466</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7106117</v>
+      </c>
+      <c r="S23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134036169</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91931</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>594612</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7106097</v>
+      </c>
+      <c r="S24" t="n">
+        <v>6</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134036154</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91945</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>594480</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7106126</v>
+      </c>
+      <c r="S25" t="n">
+        <v>28</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
         <is>
           <t>11:18</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
         <is>
           <t>11:18</t>
         </is>
       </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr">
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134040814</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91927</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>594524</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7106181</v>
+      </c>
+      <c r="S26" t="n">
+        <v>8</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134036168</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>594610</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7106086</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt. Med apotecier</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134040815</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>594571</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7106182</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134040807</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>594496</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7106021</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134036147</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80439</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>594500</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7106009</v>
+      </c>
+      <c r="S30" t="n">
+        <v>17</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134040822</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99170</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>594708</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7106124</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134036161</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80343</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>594560</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7106080</v>
+      </c>
+      <c r="S32" t="n">
+        <v>48</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134040805</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80475</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>594524</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7106017</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134036151</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91931</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>594482</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7106077</v>
+      </c>
+      <c r="S34" t="n">
+        <v>24</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134036157</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80343</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>594474</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7106125</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134040821</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99170</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>594701</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7106149</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134040827</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92235</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>658</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>594535</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7106124</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134040825</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>594826</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7106126</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134036165</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80475</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>594602</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7106101</v>
+      </c>
+      <c r="S39" t="n">
+        <v>9</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134036173</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99170</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>594691</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7106160</v>
+      </c>
+      <c r="S40" t="n">
+        <v>63</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134041932</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Åsele Söndag Inventering, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>594484</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7106025</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134040824</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80343</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>594761</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7106145</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134040828</v>
+      </c>
+      <c r="B43" t="n">
+        <v>92396</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>594548</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7106114</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134041933</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80475</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Åsele Söndag Inventering, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>594496</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7106047</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134036146</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92396</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>594500</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7106009</v>
+      </c>
+      <c r="S45" t="n">
+        <v>64</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134036177</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92659</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>594739</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7106142</v>
+      </c>
+      <c r="S46" t="n">
+        <v>48</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134036150</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>594479</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7106056</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>134036171</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91945</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>594612</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7106094</v>
+      </c>
+      <c r="S48" t="n">
+        <v>7</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>134036170</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>898</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>594612</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7106097</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>134040809</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91945</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>594482</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7106066</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>134036179</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91931</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>594582</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7106116</v>
+      </c>
+      <c r="S51" t="n">
+        <v>12</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>134036158</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98019</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>594476</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7106135</v>
+      </c>
+      <c r="S52" t="n">
+        <v>6</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>134036152</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80439</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>594475</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7106098</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>134041938</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91927</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Åsele Söndag Inventering, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>594721</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7106166</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>134040817</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>594576</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7106159</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>134036163</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>594604</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7106104</v>
+      </c>
+      <c r="S56" t="n">
+        <v>24</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>134036175</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91951</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>594758</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7106168</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>134040818</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91927</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>594598</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7106142</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>134041937</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91927</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Åsele Söndag Inventering, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>594714</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7106130</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>134036145</v>
+      </c>
+      <c r="B60" t="n">
+        <v>91931</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>594513</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7106004</v>
+      </c>
+      <c r="S60" t="n">
+        <v>18</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>

--- a/artfynd/A 2278-2026 artfynd.xlsx
+++ b/artfynd/A 2278-2026 artfynd.xlsx
@@ -3713,48 +3713,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134036147</v>
+        <v>134040822</v>
       </c>
       <c r="B30" t="n">
-        <v>80439</v>
+        <v>99170</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>594500</v>
+        <v>594708</v>
       </c>
       <c r="R30" t="n">
-        <v>7106009</v>
+        <v>7106124</v>
       </c>
       <c r="S30" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3802,18 +3802,19 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3824,48 +3825,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134040822</v>
+        <v>134036147</v>
       </c>
       <c r="B31" t="n">
-        <v>99170</v>
+        <v>80439</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>594708</v>
+        <v>594500</v>
       </c>
       <c r="R31" t="n">
-        <v>7106124</v>
+        <v>7106009</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3894,7 +3895,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3904,7 +3905,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3913,19 +3914,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4159,48 +4159,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134036151</v>
+        <v>134040821</v>
       </c>
       <c r="B34" t="n">
-        <v>91931</v>
+        <v>99170</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>594482</v>
+        <v>594701</v>
       </c>
       <c r="R34" t="n">
-        <v>7106077</v>
+        <v>7106149</v>
       </c>
       <c r="S34" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4254,12 +4254,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4270,45 +4270,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134036157</v>
+        <v>134040827</v>
       </c>
       <c r="B35" t="n">
-        <v>80343</v>
+        <v>92235</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>594474</v>
+        <v>594535</v>
       </c>
       <c r="R35" t="n">
-        <v>7106125</v>
+        <v>7106124</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4365,12 +4365,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4381,48 +4381,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134040821</v>
+        <v>134036151</v>
       </c>
       <c r="B36" t="n">
-        <v>99170</v>
+        <v>91931</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>594701</v>
+        <v>594482</v>
       </c>
       <c r="R36" t="n">
-        <v>7106149</v>
+        <v>7106077</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4476,12 +4476,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4492,45 +4492,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134040827</v>
+        <v>134036157</v>
       </c>
       <c r="B37" t="n">
-        <v>92235</v>
+        <v>80343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>594535</v>
+        <v>594474</v>
       </c>
       <c r="R37" t="n">
-        <v>7106124</v>
+        <v>7106125</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4587,12 +4587,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4603,48 +4603,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134040825</v>
+        <v>134036165</v>
       </c>
       <c r="B38" t="n">
-        <v>79334</v>
+        <v>80475</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>594826</v>
+        <v>594602</v>
       </c>
       <c r="R38" t="n">
-        <v>7106126</v>
+        <v>7106101</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4698,12 +4698,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4714,48 +4714,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134036165</v>
+        <v>134040825</v>
       </c>
       <c r="B39" t="n">
-        <v>80475</v>
+        <v>79334</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>594602</v>
+        <v>594826</v>
       </c>
       <c r="R39" t="n">
-        <v>7106101</v>
+        <v>7106126</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4809,12 +4809,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4825,10 +4825,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134036173</v>
+        <v>134040824</v>
       </c>
       <c r="B40" t="n">
-        <v>99170</v>
+        <v>80343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4836,37 +4836,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>594691</v>
+        <v>594761</v>
       </c>
       <c r="R40" t="n">
-        <v>7106160</v>
+        <v>7106145</v>
       </c>
       <c r="S40" t="n">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4920,12 +4920,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4936,45 +4936,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134041932</v>
+        <v>134040828</v>
       </c>
       <c r="B41" t="n">
-        <v>80468</v>
+        <v>92396</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>594484</v>
+        <v>594548</v>
       </c>
       <c r="R41" t="n">
-        <v>7106025</v>
+        <v>7106114</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5029,6 +5029,16 @@
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+        </is>
+      </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -5037,10 +5047,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134040824</v>
+        <v>134041932</v>
       </c>
       <c r="B42" t="n">
-        <v>80343</v>
+        <v>80468</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5048,34 +5058,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>594761</v>
+        <v>594484</v>
       </c>
       <c r="R42" t="n">
-        <v>7106145</v>
+        <v>7106025</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5107,7 +5117,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5117,7 +5127,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5130,16 +5140,6 @@
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
-        </is>
-      </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -5148,48 +5148,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134040828</v>
+        <v>134036173</v>
       </c>
       <c r="B43" t="n">
-        <v>92396</v>
+        <v>99170</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>594548</v>
+        <v>594691</v>
       </c>
       <c r="R43" t="n">
-        <v>7106114</v>
+        <v>7106160</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5243,12 +5243,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5259,48 +5259,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134041933</v>
+        <v>134036146</v>
       </c>
       <c r="B44" t="n">
-        <v>80475</v>
+        <v>92396</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>594496</v>
+        <v>594500</v>
       </c>
       <c r="R44" t="n">
-        <v>7106047</v>
+        <v>7106009</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5352,6 +5352,16 @@
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -5360,32 +5370,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134036146</v>
+        <v>134036177</v>
       </c>
       <c r="B45" t="n">
-        <v>92396</v>
+        <v>92659</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5395,13 +5405,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>594500</v>
+        <v>594739</v>
       </c>
       <c r="R45" t="n">
-        <v>7106009</v>
+        <v>7106142</v>
       </c>
       <c r="S45" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5430,7 +5440,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5440,7 +5450,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5471,48 +5481,56 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134036177</v>
+        <v>134036150</v>
       </c>
       <c r="B46" t="n">
-        <v>92659</v>
+        <v>57958</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>594739</v>
+        <v>594479</v>
       </c>
       <c r="R46" t="n">
-        <v>7106142</v>
+        <v>7106056</v>
       </c>
       <c r="S46" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5541,7 +5559,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5551,14 +5569,14 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG46" t="b">
         <v>0</v>
@@ -5582,53 +5600,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134036150</v>
+        <v>134041933</v>
       </c>
       <c r="B47" t="n">
-        <v>57958</v>
+        <v>80475</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>594479</v>
+        <v>594496</v>
       </c>
       <c r="R47" t="n">
-        <v>7106056</v>
+        <v>7106047</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5660,7 +5670,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5670,29 +5680,19 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
-        </is>
-      </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>

--- a/artfynd/A 2278-2026 artfynd.xlsx
+++ b/artfynd/A 2278-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134004111</v>
+        <v>134005846</v>
       </c>
       <c r="B8" t="n">
         <v>79334</v>
@@ -1338,17 +1338,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>a 2278-2026, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594815</v>
+        <v>594599</v>
       </c>
       <c r="R8" t="n">
-        <v>7106147</v>
+        <v>7106170</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1400,15 +1400,11 @@
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134005846</v>
+        <v>134004111</v>
       </c>
       <c r="B9" t="n">
         <v>79334</v>
@@ -1439,17 +1435,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>a 2278-2026, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594599</v>
+        <v>594815</v>
       </c>
       <c r="R9" t="n">
-        <v>7106170</v>
+        <v>7106147</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1478,7 +1474,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1488,7 +1484,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,7 +1497,11 @@
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134036149</v>
+        <v>134041934</v>
       </c>
       <c r="B16" t="n">
-        <v>57955</v>
+        <v>91951</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2182,37 +2182,33 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594477</v>
+        <v>594559</v>
       </c>
       <c r="R16" t="n">
-        <v>7106037</v>
+        <v>7106144</v>
       </c>
       <c r="S16" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2241,7 +2237,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2251,7 +2247,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2264,16 +2260,6 @@
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
-        </is>
-      </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -2282,10 +2268,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134041934</v>
+        <v>134036149</v>
       </c>
       <c r="B17" t="n">
-        <v>91951</v>
+        <v>57955</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2293,33 +2279,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594559</v>
+        <v>594477</v>
       </c>
       <c r="R17" t="n">
-        <v>7106144</v>
+        <v>7106037</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2348,7 +2338,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2358,7 +2348,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2371,6 +2361,16 @@
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -4159,48 +4159,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134040821</v>
+        <v>134036151</v>
       </c>
       <c r="B34" t="n">
-        <v>99170</v>
+        <v>91931</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>594701</v>
+        <v>594482</v>
       </c>
       <c r="R34" t="n">
-        <v>7106149</v>
+        <v>7106077</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4254,12 +4254,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4270,45 +4270,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134040827</v>
+        <v>134036157</v>
       </c>
       <c r="B35" t="n">
-        <v>92235</v>
+        <v>80343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>594535</v>
+        <v>594474</v>
       </c>
       <c r="R35" t="n">
-        <v>7106124</v>
+        <v>7106125</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4365,12 +4365,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4381,48 +4381,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134036151</v>
+        <v>134040821</v>
       </c>
       <c r="B36" t="n">
-        <v>91931</v>
+        <v>99170</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>594482</v>
+        <v>594701</v>
       </c>
       <c r="R36" t="n">
-        <v>7106077</v>
+        <v>7106149</v>
       </c>
       <c r="S36" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4476,12 +4476,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4492,45 +4492,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134036157</v>
+        <v>134040827</v>
       </c>
       <c r="B37" t="n">
-        <v>80343</v>
+        <v>92235</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>594474</v>
+        <v>594535</v>
       </c>
       <c r="R37" t="n">
-        <v>7106125</v>
+        <v>7106124</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4587,12 +4587,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -6034,10 +6034,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134036179</v>
+        <v>134041938</v>
       </c>
       <c r="B51" t="n">
-        <v>91931</v>
+        <v>91927</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6045,37 +6045,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>594582</v>
+        <v>594721</v>
       </c>
       <c r="R51" t="n">
-        <v>7106116</v>
+        <v>7106166</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6127,16 +6127,6 @@
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
-        </is>
-      </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -6145,32 +6135,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134036158</v>
+        <v>134036179</v>
       </c>
       <c r="B52" t="n">
-        <v>98019</v>
+        <v>91931</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6180,13 +6170,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>594476</v>
+        <v>594582</v>
       </c>
       <c r="R52" t="n">
-        <v>7106135</v>
+        <v>7106116</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6215,7 +6205,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6225,7 +6215,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6256,32 +6246,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134036152</v>
+        <v>134036158</v>
       </c>
       <c r="B53" t="n">
-        <v>80439</v>
+        <v>98019</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6291,13 +6281,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>594475</v>
+        <v>594476</v>
       </c>
       <c r="R53" t="n">
-        <v>7106098</v>
+        <v>7106135</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6326,7 +6316,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6336,7 +6326,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6367,10 +6357,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134041938</v>
+        <v>134036152</v>
       </c>
       <c r="B54" t="n">
-        <v>91927</v>
+        <v>80439</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6378,34 +6368,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>594721</v>
+        <v>594475</v>
       </c>
       <c r="R54" t="n">
-        <v>7106166</v>
+        <v>7106098</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6437,7 +6427,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6447,7 +6437,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6460,6 +6450,16 @@
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+        </is>
+      </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -7121,6 +7121,126 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>134086724</v>
+      </c>
+      <c r="B61" t="n">
+        <v>80452</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Fårkullen A 2278-2026, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>594543</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7106175</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Gunnar Janson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Gunnar Janson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>

--- a/artfynd/A 2278-2026 artfynd.xlsx
+++ b/artfynd/A 2278-2026 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134004110</v>
+        <v>134004112</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>80482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594497</v>
+        <v>594779</v>
       </c>
       <c r="R3" t="n">
-        <v>7106185</v>
+        <v>7106096</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,6 +880,16 @@
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -893,32 +898,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134004112</v>
+        <v>134004110</v>
       </c>
       <c r="B4" t="n">
-        <v>80468</v>
+        <v>57965</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,13 +933,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594779</v>
+        <v>594497</v>
       </c>
       <c r="R4" t="n">
-        <v>7106096</v>
+        <v>7106185</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +978,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,6 +996,16 @@
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -997,7 +1017,7 @@
         <v>134004114</v>
       </c>
       <c r="B5" t="n">
-        <v>92235</v>
+        <v>92218</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,6 +1107,16 @@
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -1098,7 +1128,7 @@
         <v>134004120</v>
       </c>
       <c r="B6" t="n">
-        <v>58822</v>
+        <v>58829</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,6 +1219,16 @@
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -1200,7 +1240,7 @@
         <v>134004119</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,6 +1339,16 @@
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -1307,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134005846</v>
+        <v>134004111</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,17 +1388,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>a 2278-2026, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594599</v>
+        <v>594815</v>
       </c>
       <c r="R8" t="n">
-        <v>7106170</v>
+        <v>7106147</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1387,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1400,14 +1450,28 @@
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134004111</v>
+        <v>134005846</v>
       </c>
       <c r="B9" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,17 +1499,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>a 2278-2026, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594815</v>
+        <v>594599</v>
       </c>
       <c r="R9" t="n">
-        <v>7106147</v>
+        <v>7106170</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1474,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1484,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1497,18 +1561,24 @@
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>134036167</v>
       </c>
       <c r="B10" t="n">
-        <v>96366</v>
+        <v>96386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1675,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1619,7 +1689,7 @@
         <v>134040810</v>
       </c>
       <c r="B11" t="n">
-        <v>80475</v>
+        <v>80489</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,7 +1786,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1730,7 +1800,7 @@
         <v>134040804</v>
       </c>
       <c r="B12" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,7 +1897,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1841,7 +1911,7 @@
         <v>134040826</v>
       </c>
       <c r="B13" t="n">
-        <v>96366</v>
+        <v>96386</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,7 +2008,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1952,7 +2022,7 @@
         <v>134040803</v>
       </c>
       <c r="B14" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2119,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2063,7 +2133,7 @@
         <v>134040813</v>
       </c>
       <c r="B15" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,7 +2230,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2171,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134041934</v>
+        <v>134036149</v>
       </c>
       <c r="B16" t="n">
-        <v>91951</v>
+        <v>57962</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2182,33 +2252,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594559</v>
+        <v>594477</v>
       </c>
       <c r="R16" t="n">
-        <v>7106144</v>
+        <v>7106037</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2237,7 +2311,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2247,7 +2321,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,6 +2334,16 @@
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+        </is>
+      </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -2268,10 +2352,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134036149</v>
+        <v>134041934</v>
       </c>
       <c r="B17" t="n">
-        <v>57955</v>
+        <v>91967</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2279,37 +2363,33 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594477</v>
+        <v>594559</v>
       </c>
       <c r="R17" t="n">
-        <v>7106037</v>
+        <v>7106144</v>
       </c>
       <c r="S17" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2338,7 +2418,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2348,7 +2428,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2363,12 +2443,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2382,7 +2462,7 @@
         <v>134036160</v>
       </c>
       <c r="B18" t="n">
-        <v>96366</v>
+        <v>96386</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2479,7 +2559,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2490,34 +2570,30 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134036172</v>
+        <v>134036159</v>
       </c>
       <c r="B19" t="n">
-        <v>80343</v>
+        <v>91967</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2525,13 +2601,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594619</v>
+        <v>594504</v>
       </c>
       <c r="R19" t="n">
-        <v>7106110</v>
+        <v>7106148</v>
       </c>
       <c r="S19" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2560,7 +2636,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2570,7 +2646,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2579,7 +2655,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2591,7 +2666,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2602,30 +2677,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134036159</v>
+        <v>134036172</v>
       </c>
       <c r="B20" t="n">
-        <v>91951</v>
+        <v>80357</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2633,13 +2712,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594504</v>
+        <v>594619</v>
       </c>
       <c r="R20" t="n">
-        <v>7106148</v>
+        <v>7106110</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2668,7 +2747,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2678,7 +2757,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2687,6 +2766,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2698,7 +2778,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2712,7 +2792,7 @@
         <v>134040806</v>
       </c>
       <c r="B21" t="n">
-        <v>91927</v>
+        <v>91943</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2809,7 +2889,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2823,7 +2903,7 @@
         <v>134040808</v>
       </c>
       <c r="B22" t="n">
-        <v>80475</v>
+        <v>80489</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +3000,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2931,32 +3011,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134036155</v>
+        <v>134036154</v>
       </c>
       <c r="B23" t="n">
-        <v>80399</v>
+        <v>91961</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,13 +3046,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594466</v>
+        <v>594480</v>
       </c>
       <c r="R23" t="n">
-        <v>7106117</v>
+        <v>7106126</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3001,7 +3081,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3011,7 +3091,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3031,7 +3111,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3045,7 +3125,7 @@
         <v>134036169</v>
       </c>
       <c r="B24" t="n">
-        <v>91931</v>
+        <v>91947</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3142,7 +3222,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3153,32 +3233,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134036154</v>
+        <v>134036155</v>
       </c>
       <c r="B25" t="n">
-        <v>91945</v>
+        <v>80413</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3188,13 +3268,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594480</v>
+        <v>594466</v>
       </c>
       <c r="R25" t="n">
-        <v>7106126</v>
+        <v>7106117</v>
       </c>
       <c r="S25" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3223,7 +3303,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3233,7 +3313,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3253,7 +3333,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3267,7 +3347,7 @@
         <v>134040814</v>
       </c>
       <c r="B26" t="n">
-        <v>91927</v>
+        <v>91943</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3364,7 +3444,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3375,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134036168</v>
+        <v>134040815</v>
       </c>
       <c r="B27" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3406,17 +3486,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594610</v>
+        <v>594571</v>
       </c>
       <c r="R27" t="n">
-        <v>7106086</v>
+        <v>7106182</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3445,7 +3525,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3455,12 +3535,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt. Med apotecier</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3475,12 +3550,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3491,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134040815</v>
+        <v>134040807</v>
       </c>
       <c r="B28" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3526,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594571</v>
+        <v>594496</v>
       </c>
       <c r="R28" t="n">
-        <v>7106182</v>
+        <v>7106021</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3561,7 +3636,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3571,7 +3646,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3591,7 +3666,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3602,10 +3677,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134040807</v>
+        <v>134036168</v>
       </c>
       <c r="B29" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3633,17 +3708,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594496</v>
+        <v>594610</v>
       </c>
       <c r="R29" t="n">
-        <v>7106021</v>
+        <v>7106086</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3672,7 +3747,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3682,7 +3757,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt. Med apotecier</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3697,12 +3777,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3716,7 +3796,7 @@
         <v>134040822</v>
       </c>
       <c r="B30" t="n">
-        <v>99170</v>
+        <v>99190</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3814,7 +3894,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3828,7 +3908,7 @@
         <v>134036147</v>
       </c>
       <c r="B31" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3925,7 +4005,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3939,7 +4019,7 @@
         <v>134036161</v>
       </c>
       <c r="B32" t="n">
-        <v>80343</v>
+        <v>80357</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4037,7 +4117,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4051,7 +4131,7 @@
         <v>134040805</v>
       </c>
       <c r="B33" t="n">
-        <v>80475</v>
+        <v>80489</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4148,7 +4228,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4159,48 +4239,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134036151</v>
+        <v>134040821</v>
       </c>
       <c r="B34" t="n">
-        <v>91931</v>
+        <v>99190</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>594482</v>
+        <v>594701</v>
       </c>
       <c r="R34" t="n">
-        <v>7106077</v>
+        <v>7106149</v>
       </c>
       <c r="S34" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4229,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4239,7 +4319,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4254,12 +4334,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4270,45 +4350,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134036157</v>
+        <v>134040827</v>
       </c>
       <c r="B35" t="n">
-        <v>80343</v>
+        <v>92218</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>594474</v>
+        <v>594535</v>
       </c>
       <c r="R35" t="n">
-        <v>7106125</v>
+        <v>7106124</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4340,7 +4420,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4350,7 +4430,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4365,12 +4445,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4381,48 +4461,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134040821</v>
+        <v>134036151</v>
       </c>
       <c r="B36" t="n">
-        <v>99170</v>
+        <v>91947</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>594701</v>
+        <v>594482</v>
       </c>
       <c r="R36" t="n">
-        <v>7106149</v>
+        <v>7106077</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4451,7 +4531,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4461,7 +4541,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4476,12 +4556,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4492,45 +4572,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134040827</v>
+        <v>134036157</v>
       </c>
       <c r="B37" t="n">
-        <v>92235</v>
+        <v>80357</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>594535</v>
+        <v>594474</v>
       </c>
       <c r="R37" t="n">
-        <v>7106124</v>
+        <v>7106125</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4562,7 +4642,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4572,7 +4652,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4587,12 +4667,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4606,7 +4686,7 @@
         <v>134036165</v>
       </c>
       <c r="B38" t="n">
-        <v>80475</v>
+        <v>80489</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4703,7 +4783,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4717,7 +4797,7 @@
         <v>134040825</v>
       </c>
       <c r="B39" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4814,7 +4894,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4828,7 +4908,7 @@
         <v>134040824</v>
       </c>
       <c r="B40" t="n">
-        <v>80343</v>
+        <v>80357</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4925,7 +5005,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4939,7 +5019,7 @@
         <v>134040828</v>
       </c>
       <c r="B41" t="n">
-        <v>92396</v>
+        <v>92379</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5036,7 +5116,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5050,7 +5130,7 @@
         <v>134041932</v>
       </c>
       <c r="B42" t="n">
-        <v>80468</v>
+        <v>80482</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5140,6 +5220,16 @@
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Katerina Shytaj</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Katerina Shytaj</t>
+        </is>
+      </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -5151,7 +5241,7 @@
         <v>134036173</v>
       </c>
       <c r="B43" t="n">
-        <v>99170</v>
+        <v>99190</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5248,7 +5338,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5259,48 +5349,56 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134036146</v>
+        <v>134036150</v>
       </c>
       <c r="B44" t="n">
-        <v>92396</v>
+        <v>57965</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>594500</v>
+        <v>594479</v>
       </c>
       <c r="R44" t="n">
-        <v>7106009</v>
+        <v>7106056</v>
       </c>
       <c r="S44" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5329,7 +5427,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5339,14 +5437,14 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG44" t="b">
         <v>0</v>
@@ -5359,7 +5457,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5370,32 +5468,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134036177</v>
+        <v>134036146</v>
       </c>
       <c r="B45" t="n">
-        <v>92659</v>
+        <v>92379</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5405,13 +5503,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>594739</v>
+        <v>594500</v>
       </c>
       <c r="R45" t="n">
-        <v>7106142</v>
+        <v>7106009</v>
       </c>
       <c r="S45" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5440,7 +5538,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5450,7 +5548,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5470,7 +5568,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5481,56 +5579,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134036150</v>
+        <v>134036177</v>
       </c>
       <c r="B46" t="n">
-        <v>57958</v>
+        <v>92172</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>594479</v>
+        <v>594739</v>
       </c>
       <c r="R46" t="n">
-        <v>7106056</v>
+        <v>7106142</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5559,7 +5649,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5569,14 +5659,14 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="b">
         <v>0</v>
@@ -5589,7 +5679,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5603,7 +5693,7 @@
         <v>134041933</v>
       </c>
       <c r="B47" t="n">
-        <v>80475</v>
+        <v>80489</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5693,6 +5783,16 @@
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Katerina Shytaj</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Katerina Shytaj</t>
+        </is>
+      </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -5701,32 +5801,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134036171</v>
+        <v>134036170</v>
       </c>
       <c r="B48" t="n">
-        <v>91945</v>
+        <v>92662</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1204</v>
+        <v>898</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5739,10 +5839,10 @@
         <v>594612</v>
       </c>
       <c r="R48" t="n">
-        <v>7106094</v>
+        <v>7106097</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5771,7 +5871,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5781,7 +5881,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5801,7 +5901,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5812,32 +5912,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134036170</v>
+        <v>134036171</v>
       </c>
       <c r="B49" t="n">
-        <v>92632</v>
+        <v>91961</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>898</v>
+        <v>1204</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5850,10 +5950,10 @@
         <v>594612</v>
       </c>
       <c r="R49" t="n">
-        <v>7106097</v>
+        <v>7106094</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5882,7 +5982,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5892,7 +5992,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5912,7 +6012,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5926,7 +6026,7 @@
         <v>134040809</v>
       </c>
       <c r="B50" t="n">
-        <v>91945</v>
+        <v>91961</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6023,7 +6123,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6034,48 +6134,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134041938</v>
+        <v>134036158</v>
       </c>
       <c r="B51" t="n">
-        <v>91927</v>
+        <v>98039</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>221941</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>594721</v>
+        <v>594476</v>
       </c>
       <c r="R51" t="n">
-        <v>7106166</v>
+        <v>7106135</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6104,7 +6204,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6114,7 +6214,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6127,6 +6227,16 @@
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+        </is>
+      </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -6138,7 +6248,7 @@
         <v>134036179</v>
       </c>
       <c r="B52" t="n">
-        <v>91931</v>
+        <v>91947</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6235,7 +6345,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6246,32 +6356,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134036158</v>
+        <v>134036152</v>
       </c>
       <c r="B53" t="n">
-        <v>98019</v>
+        <v>80453</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6281,13 +6391,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>594476</v>
+        <v>594475</v>
       </c>
       <c r="R53" t="n">
-        <v>7106135</v>
+        <v>7106098</v>
       </c>
       <c r="S53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6316,7 +6426,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6326,7 +6436,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6346,7 +6456,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6357,10 +6467,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134036152</v>
+        <v>134041938</v>
       </c>
       <c r="B54" t="n">
-        <v>80439</v>
+        <v>91943</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6368,34 +6478,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>594475</v>
+        <v>594721</v>
       </c>
       <c r="R54" t="n">
-        <v>7106098</v>
+        <v>7106166</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6427,7 +6537,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6437,7 +6547,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6452,12 +6562,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6471,7 +6581,7 @@
         <v>134040817</v>
       </c>
       <c r="B55" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6576,7 +6686,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6587,48 +6697,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134036163</v>
+        <v>134040818</v>
       </c>
       <c r="B56" t="n">
-        <v>80468</v>
+        <v>91943</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>594604</v>
+        <v>594598</v>
       </c>
       <c r="R56" t="n">
-        <v>7106104</v>
+        <v>7106142</v>
       </c>
       <c r="S56" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6657,7 +6767,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6667,7 +6777,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6682,12 +6792,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6701,7 +6811,7 @@
         <v>134036175</v>
       </c>
       <c r="B57" t="n">
-        <v>91951</v>
+        <v>91967</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6794,7 +6904,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6805,48 +6915,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134040818</v>
+        <v>134036163</v>
       </c>
       <c r="B58" t="n">
-        <v>91927</v>
+        <v>80482</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>594598</v>
+        <v>594604</v>
       </c>
       <c r="R58" t="n">
-        <v>7106142</v>
+        <v>7106104</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6875,7 +6985,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6885,7 +6995,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6900,12 +7010,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Gunnar Janson, Maria  Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6916,10 +7026,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134041937</v>
+        <v>134036145</v>
       </c>
       <c r="B59" t="n">
-        <v>91927</v>
+        <v>91947</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6927,37 +7037,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>594714</v>
+        <v>594513</v>
       </c>
       <c r="R59" t="n">
-        <v>7106130</v>
+        <v>7106004</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6986,7 +7096,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6996,7 +7106,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7009,6 +7119,16 @@
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+        </is>
+      </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -7017,10 +7137,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134036145</v>
+        <v>134041937</v>
       </c>
       <c r="B60" t="n">
-        <v>91931</v>
+        <v>91943</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7028,37 +7148,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>594513</v>
+        <v>594714</v>
       </c>
       <c r="R60" t="n">
-        <v>7106004</v>
+        <v>7106130</v>
       </c>
       <c r="S60" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7087,7 +7207,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7097,7 +7217,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7112,12 +7232,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7131,7 +7251,7 @@
         <v>134086724</v>
       </c>
       <c r="B61" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 2278-2026 artfynd.xlsx
+++ b/artfynd/A 2278-2026 artfynd.xlsx
@@ -2570,30 +2570,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134036159</v>
+        <v>134036172</v>
       </c>
       <c r="B19" t="n">
-        <v>91967</v>
+        <v>80357</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2601,13 +2605,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594504</v>
+        <v>594619</v>
       </c>
       <c r="R19" t="n">
-        <v>7106148</v>
+        <v>7106110</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2636,7 +2640,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2646,7 +2650,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2655,6 +2659,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2677,34 +2682,30 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134036172</v>
+        <v>134036159</v>
       </c>
       <c r="B20" t="n">
-        <v>80357</v>
+        <v>91967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2712,13 +2713,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594619</v>
+        <v>594504</v>
       </c>
       <c r="R20" t="n">
-        <v>7106110</v>
+        <v>7106148</v>
       </c>
       <c r="S20" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2747,7 +2748,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2757,7 +2758,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2766,7 +2767,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3011,10 +3011,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134036154</v>
+        <v>134040814</v>
       </c>
       <c r="B23" t="n">
-        <v>91961</v>
+        <v>91943</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3022,37 +3022,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594480</v>
+        <v>594524</v>
       </c>
       <c r="R23" t="n">
-        <v>7106126</v>
+        <v>7106181</v>
       </c>
       <c r="S23" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3106,12 +3106,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3122,10 +3122,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134036169</v>
+        <v>134036154</v>
       </c>
       <c r="B24" t="n">
-        <v>91947</v>
+        <v>91961</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,21 +3133,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3157,13 +3157,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594612</v>
+        <v>594480</v>
       </c>
       <c r="R24" t="n">
-        <v>7106097</v>
+        <v>7106126</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3233,32 +3233,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134036155</v>
+        <v>134036169</v>
       </c>
       <c r="B25" t="n">
-        <v>80413</v>
+        <v>91947</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3268,13 +3268,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594466</v>
+        <v>594612</v>
       </c>
       <c r="R25" t="n">
-        <v>7106117</v>
+        <v>7106097</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3344,45 +3344,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134040814</v>
+        <v>134036155</v>
       </c>
       <c r="B26" t="n">
-        <v>91943</v>
+        <v>80413</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594524</v>
+        <v>594466</v>
       </c>
       <c r="R26" t="n">
-        <v>7106181</v>
+        <v>7106117</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3439,12 +3439,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3455,7 +3455,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134040815</v>
+        <v>134036168</v>
       </c>
       <c r="B27" t="n">
         <v>79348</v>
@@ -3486,17 +3486,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594571</v>
+        <v>594610</v>
       </c>
       <c r="R27" t="n">
-        <v>7106182</v>
+        <v>7106086</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3535,7 +3535,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt. Med apotecier</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3550,12 +3555,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3566,7 +3571,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134040807</v>
+        <v>134040815</v>
       </c>
       <c r="B28" t="n">
         <v>79348</v>
@@ -3601,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594496</v>
+        <v>594571</v>
       </c>
       <c r="R28" t="n">
-        <v>7106021</v>
+        <v>7106182</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3636,7 +3641,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3646,7 +3651,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3677,7 +3682,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134036168</v>
+        <v>134040807</v>
       </c>
       <c r="B29" t="n">
         <v>79348</v>
@@ -3708,17 +3713,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594610</v>
+        <v>594496</v>
       </c>
       <c r="R29" t="n">
-        <v>7106086</v>
+        <v>7106021</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3747,7 +3752,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3757,12 +3762,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt. Med apotecier</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3777,12 +3777,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -4239,48 +4239,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134040821</v>
+        <v>134036151</v>
       </c>
       <c r="B34" t="n">
-        <v>99190</v>
+        <v>91947</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>594701</v>
+        <v>594482</v>
       </c>
       <c r="R34" t="n">
-        <v>7106149</v>
+        <v>7106077</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4334,12 +4334,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4350,45 +4350,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134040827</v>
+        <v>134036157</v>
       </c>
       <c r="B35" t="n">
-        <v>92218</v>
+        <v>80357</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>594535</v>
+        <v>594474</v>
       </c>
       <c r="R35" t="n">
-        <v>7106124</v>
+        <v>7106125</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4445,12 +4445,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4461,48 +4461,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134036151</v>
+        <v>134040821</v>
       </c>
       <c r="B36" t="n">
-        <v>91947</v>
+        <v>99190</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>594482</v>
+        <v>594701</v>
       </c>
       <c r="R36" t="n">
-        <v>7106077</v>
+        <v>7106149</v>
       </c>
       <c r="S36" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4556,12 +4556,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4572,45 +4572,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134036157</v>
+        <v>134040827</v>
       </c>
       <c r="B37" t="n">
-        <v>80357</v>
+        <v>92218</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>594474</v>
+        <v>594535</v>
       </c>
       <c r="R37" t="n">
-        <v>7106125</v>
+        <v>7106124</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,12 +4667,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4905,10 +4905,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134040824</v>
+        <v>134041932</v>
       </c>
       <c r="B40" t="n">
-        <v>80357</v>
+        <v>80482</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4916,34 +4916,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>594761</v>
+        <v>594484</v>
       </c>
       <c r="R40" t="n">
-        <v>7106145</v>
+        <v>7106025</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5000,12 +5000,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5016,48 +5016,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134040828</v>
+        <v>134036173</v>
       </c>
       <c r="B41" t="n">
-        <v>92379</v>
+        <v>99190</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>594548</v>
+        <v>594691</v>
       </c>
       <c r="R41" t="n">
-        <v>7106114</v>
+        <v>7106160</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5111,12 +5111,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5127,10 +5127,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134041932</v>
+        <v>134040824</v>
       </c>
       <c r="B42" t="n">
-        <v>80482</v>
+        <v>80357</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5138,34 +5138,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>594484</v>
+        <v>594761</v>
       </c>
       <c r="R42" t="n">
-        <v>7106025</v>
+        <v>7106145</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5222,12 +5222,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5238,48 +5238,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134036173</v>
+        <v>134040828</v>
       </c>
       <c r="B43" t="n">
-        <v>99190</v>
+        <v>92379</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>594691</v>
+        <v>594548</v>
       </c>
       <c r="R43" t="n">
-        <v>7106160</v>
+        <v>7106114</v>
       </c>
       <c r="S43" t="n">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5333,12 +5333,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5349,56 +5349,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134036150</v>
+        <v>134036177</v>
       </c>
       <c r="B44" t="n">
-        <v>57965</v>
+        <v>92172</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>594479</v>
+        <v>594739</v>
       </c>
       <c r="R44" t="n">
-        <v>7106056</v>
+        <v>7106142</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5427,7 +5419,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5437,14 +5429,14 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="b">
         <v>0</v>
@@ -5579,10 +5571,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134036177</v>
+        <v>134041933</v>
       </c>
       <c r="B46" t="n">
-        <v>92172</v>
+        <v>80489</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5590,37 +5582,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>594739</v>
+        <v>594496</v>
       </c>
       <c r="R46" t="n">
-        <v>7106142</v>
+        <v>7106047</v>
       </c>
       <c r="S46" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5649,7 +5641,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5659,7 +5651,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5674,12 +5666,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5690,45 +5682,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134041933</v>
+        <v>134036150</v>
       </c>
       <c r="B47" t="n">
-        <v>80489</v>
+        <v>57965</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>594496</v>
+        <v>594479</v>
       </c>
       <c r="R47" t="n">
-        <v>7106047</v>
+        <v>7106056</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5770,14 +5770,14 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG47" t="b">
         <v>0</v>
@@ -5785,12 +5785,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -6134,32 +6134,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134036158</v>
+        <v>134036179</v>
       </c>
       <c r="B51" t="n">
-        <v>98039</v>
+        <v>91947</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6169,13 +6169,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>594476</v>
+        <v>594582</v>
       </c>
       <c r="R51" t="n">
-        <v>7106135</v>
+        <v>7106116</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6245,10 +6245,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134036179</v>
+        <v>134036152</v>
       </c>
       <c r="B52" t="n">
-        <v>91947</v>
+        <v>80453</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6256,21 +6256,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6280,13 +6280,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>594582</v>
+        <v>594475</v>
       </c>
       <c r="R52" t="n">
-        <v>7106116</v>
+        <v>7106098</v>
       </c>
       <c r="S52" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6356,10 +6356,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134036152</v>
+        <v>134041938</v>
       </c>
       <c r="B53" t="n">
-        <v>80453</v>
+        <v>91943</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6367,34 +6367,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>594475</v>
+        <v>594721</v>
       </c>
       <c r="R53" t="n">
-        <v>7106098</v>
+        <v>7106166</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6451,12 +6451,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6467,48 +6467,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134041938</v>
+        <v>134036158</v>
       </c>
       <c r="B54" t="n">
-        <v>91943</v>
+        <v>98039</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>221941</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>594721</v>
+        <v>594476</v>
       </c>
       <c r="R54" t="n">
-        <v>7106166</v>
+        <v>7106135</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6562,12 +6562,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6697,10 +6697,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134040818</v>
+        <v>134036175</v>
       </c>
       <c r="B56" t="n">
-        <v>91943</v>
+        <v>91967</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6708,37 +6708,33 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>594598</v>
+        <v>594758</v>
       </c>
       <c r="R56" t="n">
-        <v>7106142</v>
+        <v>7106168</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6767,7 +6763,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6777,7 +6773,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6792,12 +6788,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6808,30 +6804,34 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134036175</v>
+        <v>134036163</v>
       </c>
       <c r="B57" t="n">
-        <v>91967</v>
+        <v>80482</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6839,13 +6839,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>594758</v>
+        <v>594604</v>
       </c>
       <c r="R57" t="n">
-        <v>7106168</v>
+        <v>7106104</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6915,48 +6915,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134036163</v>
+        <v>134040818</v>
       </c>
       <c r="B58" t="n">
-        <v>80482</v>
+        <v>91943</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>594604</v>
+        <v>594598</v>
       </c>
       <c r="R58" t="n">
-        <v>7106104</v>
+        <v>7106142</v>
       </c>
       <c r="S58" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7010,12 +7010,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">

--- a/artfynd/A 2278-2026 artfynd.xlsx
+++ b/artfynd/A 2278-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>134004112</v>
       </c>
       <c r="B3" t="n">
-        <v>80482</v>
+        <v>80478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>134004110</v>
       </c>
       <c r="B4" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>134004114</v>
       </c>
       <c r="B5" t="n">
-        <v>92218</v>
+        <v>92228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>134004120</v>
       </c>
       <c r="B6" t="n">
-        <v>58829</v>
+        <v>58839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>134004119</v>
       </c>
       <c r="B7" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134004111</v>
+        <v>134005846</v>
       </c>
       <c r="B8" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,17 +1388,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>a 2278-2026, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594815</v>
+        <v>594599</v>
       </c>
       <c r="R8" t="n">
-        <v>7106147</v>
+        <v>7106170</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,26 +1452,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Patrik Eriksson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134005846</v>
+        <v>134004111</v>
       </c>
       <c r="B9" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,17 +1495,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>a 2278-2026, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594599</v>
+        <v>594815</v>
       </c>
       <c r="R9" t="n">
-        <v>7106170</v>
+        <v>7106147</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,22 +1559,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134036167</v>
+        <v>134040810</v>
       </c>
       <c r="B10" t="n">
-        <v>96386</v>
+        <v>80485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,37 +1586,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594607</v>
+        <v>594501</v>
       </c>
       <c r="R10" t="n">
-        <v>7106088</v>
+        <v>7106169</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,12 +1670,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1686,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134040810</v>
+        <v>134036167</v>
       </c>
       <c r="B11" t="n">
-        <v>80489</v>
+        <v>96396</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,37 +1697,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594501</v>
+        <v>594607</v>
       </c>
       <c r="R11" t="n">
-        <v>7106169</v>
+        <v>7106088</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,12 +1781,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1800,7 +1800,7 @@
         <v>134040804</v>
       </c>
       <c r="B12" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>134040826</v>
       </c>
       <c r="B13" t="n">
-        <v>96386</v>
+        <v>96396</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>134040803</v>
       </c>
       <c r="B14" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>134040813</v>
       </c>
       <c r="B15" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134036149</v>
+        <v>134041934</v>
       </c>
       <c r="B16" t="n">
-        <v>57962</v>
+        <v>91977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,37 +2252,33 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594477</v>
+        <v>594559</v>
       </c>
       <c r="R16" t="n">
-        <v>7106037</v>
+        <v>7106144</v>
       </c>
       <c r="S16" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2311,7 +2307,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2321,7 +2317,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,12 +2332,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2352,10 +2348,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134041934</v>
+        <v>134036149</v>
       </c>
       <c r="B17" t="n">
-        <v>91967</v>
+        <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2363,33 +2359,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594559</v>
+        <v>594477</v>
       </c>
       <c r="R17" t="n">
-        <v>7106144</v>
+        <v>7106037</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2443,12 +2443,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2462,7 +2462,7 @@
         <v>134036160</v>
       </c>
       <c r="B18" t="n">
-        <v>96386</v>
+        <v>96396</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,34 +2570,30 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134036172</v>
+        <v>134036159</v>
       </c>
       <c r="B19" t="n">
-        <v>80357</v>
+        <v>91977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2605,13 +2601,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594619</v>
+        <v>594504</v>
       </c>
       <c r="R19" t="n">
-        <v>7106110</v>
+        <v>7106148</v>
       </c>
       <c r="S19" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2640,7 +2636,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2650,7 +2646,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2659,7 +2655,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2682,30 +2677,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134036159</v>
+        <v>134036172</v>
       </c>
       <c r="B20" t="n">
-        <v>91967</v>
+        <v>80367</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2713,13 +2712,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594504</v>
+        <v>594619</v>
       </c>
       <c r="R20" t="n">
-        <v>7106148</v>
+        <v>7106110</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2748,7 +2747,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2758,7 +2757,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2767,6 +2766,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>134040806</v>
       </c>
       <c r="B21" t="n">
-        <v>91943</v>
+        <v>91953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>134040808</v>
       </c>
       <c r="B22" t="n">
-        <v>80489</v>
+        <v>80485</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>134040814</v>
       </c>
       <c r="B23" t="n">
-        <v>91943</v>
+        <v>91953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>134036154</v>
       </c>
       <c r="B24" t="n">
-        <v>91961</v>
+        <v>91971</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>134036169</v>
       </c>
       <c r="B25" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>134036155</v>
       </c>
       <c r="B26" t="n">
-        <v>80413</v>
+        <v>80423</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134036168</v>
+        <v>134040815</v>
       </c>
       <c r="B27" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3486,17 +3486,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594610</v>
+        <v>594571</v>
       </c>
       <c r="R27" t="n">
-        <v>7106086</v>
+        <v>7106182</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3535,12 +3535,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt. Med apotecier</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3555,12 +3550,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3571,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134040815</v>
+        <v>134040807</v>
       </c>
       <c r="B28" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3606,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594571</v>
+        <v>594496</v>
       </c>
       <c r="R28" t="n">
-        <v>7106182</v>
+        <v>7106021</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3641,7 +3636,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3651,7 +3646,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3682,10 +3677,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134040807</v>
+        <v>134036168</v>
       </c>
       <c r="B29" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3713,17 +3708,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594496</v>
+        <v>594610</v>
       </c>
       <c r="R29" t="n">
-        <v>7106021</v>
+        <v>7106086</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3752,7 +3747,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3762,7 +3757,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt. Med apotecier</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3777,12 +3777,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3793,48 +3793,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134040822</v>
+        <v>134036147</v>
       </c>
       <c r="B30" t="n">
-        <v>99190</v>
+        <v>80473</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>594708</v>
+        <v>594500</v>
       </c>
       <c r="R30" t="n">
-        <v>7106124</v>
+        <v>7106009</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3882,19 +3882,18 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3905,48 +3904,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134036147</v>
+        <v>134040822</v>
       </c>
       <c r="B31" t="n">
-        <v>80453</v>
+        <v>99200</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>594500</v>
+        <v>594708</v>
       </c>
       <c r="R31" t="n">
-        <v>7106009</v>
+        <v>7106124</v>
       </c>
       <c r="S31" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3975,7 +3974,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3985,7 +3984,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3994,18 +3993,19 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4019,7 +4019,7 @@
         <v>134036161</v>
       </c>
       <c r="B32" t="n">
-        <v>80357</v>
+        <v>80367</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>134040805</v>
       </c>
       <c r="B33" t="n">
-        <v>80489</v>
+        <v>80485</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4239,48 +4239,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134036151</v>
+        <v>134040821</v>
       </c>
       <c r="B34" t="n">
-        <v>91947</v>
+        <v>99200</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>594482</v>
+        <v>594701</v>
       </c>
       <c r="R34" t="n">
-        <v>7106077</v>
+        <v>7106149</v>
       </c>
       <c r="S34" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4334,12 +4334,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4350,45 +4350,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134036157</v>
+        <v>134040827</v>
       </c>
       <c r="B35" t="n">
-        <v>80357</v>
+        <v>92228</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>594474</v>
+        <v>594535</v>
       </c>
       <c r="R35" t="n">
-        <v>7106125</v>
+        <v>7106124</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4445,12 +4445,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4461,48 +4461,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134040821</v>
+        <v>134036151</v>
       </c>
       <c r="B36" t="n">
-        <v>99190</v>
+        <v>91957</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>594701</v>
+        <v>594482</v>
       </c>
       <c r="R36" t="n">
-        <v>7106149</v>
+        <v>7106077</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4556,12 +4556,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4572,45 +4572,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134040827</v>
+        <v>134036157</v>
       </c>
       <c r="B37" t="n">
-        <v>92218</v>
+        <v>80367</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>594535</v>
+        <v>594474</v>
       </c>
       <c r="R37" t="n">
-        <v>7106124</v>
+        <v>7106125</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,12 +4667,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4683,48 +4683,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134036165</v>
+        <v>134040825</v>
       </c>
       <c r="B38" t="n">
-        <v>80489</v>
+        <v>79358</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>594602</v>
+        <v>594826</v>
       </c>
       <c r="R38" t="n">
-        <v>7106101</v>
+        <v>7106126</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4778,12 +4778,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4794,48 +4794,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134040825</v>
+        <v>134036165</v>
       </c>
       <c r="B39" t="n">
-        <v>79348</v>
+        <v>80485</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>594826</v>
+        <v>594602</v>
       </c>
       <c r="R39" t="n">
-        <v>7106126</v>
+        <v>7106101</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4889,12 +4889,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4908,7 +4908,7 @@
         <v>134041932</v>
       </c>
       <c r="B40" t="n">
-        <v>80482</v>
+        <v>80478</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>134036173</v>
       </c>
       <c r="B41" t="n">
-        <v>99190</v>
+        <v>99200</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>134040824</v>
       </c>
       <c r="B42" t="n">
-        <v>80357</v>
+        <v>80367</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>134040828</v>
       </c>
       <c r="B43" t="n">
-        <v>92379</v>
+        <v>92389</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5349,48 +5349,56 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134036177</v>
+        <v>134036150</v>
       </c>
       <c r="B44" t="n">
-        <v>92172</v>
+        <v>57975</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>594739</v>
+        <v>594479</v>
       </c>
       <c r="R44" t="n">
-        <v>7106142</v>
+        <v>7106056</v>
       </c>
       <c r="S44" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5419,7 +5427,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5429,14 +5437,14 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG44" t="b">
         <v>0</v>
@@ -5463,7 +5471,7 @@
         <v>134036146</v>
       </c>
       <c r="B45" t="n">
-        <v>92379</v>
+        <v>92389</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5571,10 +5579,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134041933</v>
+        <v>134036177</v>
       </c>
       <c r="B46" t="n">
-        <v>80489</v>
+        <v>92182</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5582,37 +5590,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>594496</v>
+        <v>594739</v>
       </c>
       <c r="R46" t="n">
-        <v>7106047</v>
+        <v>7106142</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5641,7 +5649,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5651,7 +5659,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5666,12 +5674,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5682,53 +5690,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134036150</v>
+        <v>134041933</v>
       </c>
       <c r="B47" t="n">
-        <v>57965</v>
+        <v>80485</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>594479</v>
+        <v>594496</v>
       </c>
       <c r="R47" t="n">
-        <v>7106056</v>
+        <v>7106047</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5770,14 +5770,14 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="b">
         <v>0</v>
@@ -5785,12 +5785,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5804,7 +5804,7 @@
         <v>134036170</v>
       </c>
       <c r="B48" t="n">
-        <v>92662</v>
+        <v>92672</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>134036171</v>
       </c>
       <c r="B49" t="n">
-        <v>91961</v>
+        <v>91971</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>134040809</v>
       </c>
       <c r="B50" t="n">
-        <v>91961</v>
+        <v>91971</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6134,10 +6134,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134036179</v>
+        <v>134041938</v>
       </c>
       <c r="B51" t="n">
-        <v>91947</v>
+        <v>91953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6145,37 +6145,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>594582</v>
+        <v>594721</v>
       </c>
       <c r="R51" t="n">
-        <v>7106116</v>
+        <v>7106166</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6229,12 +6229,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6245,32 +6245,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134036152</v>
+        <v>134036158</v>
       </c>
       <c r="B52" t="n">
-        <v>80453</v>
+        <v>98049</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6280,13 +6280,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>594475</v>
+        <v>594476</v>
       </c>
       <c r="R52" t="n">
-        <v>7106098</v>
+        <v>7106135</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6356,10 +6356,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134041938</v>
+        <v>134036179</v>
       </c>
       <c r="B53" t="n">
-        <v>91943</v>
+        <v>91957</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6367,37 +6367,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>594721</v>
+        <v>594582</v>
       </c>
       <c r="R53" t="n">
-        <v>7106166</v>
+        <v>7106116</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6451,12 +6451,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6467,32 +6467,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134036158</v>
+        <v>134036152</v>
       </c>
       <c r="B54" t="n">
-        <v>98039</v>
+        <v>80473</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6502,13 +6502,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>594476</v>
+        <v>594475</v>
       </c>
       <c r="R54" t="n">
-        <v>7106135</v>
+        <v>7106098</v>
       </c>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6581,7 +6581,7 @@
         <v>134040817</v>
       </c>
       <c r="B55" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>134036175</v>
       </c>
       <c r="B56" t="n">
-        <v>91967</v>
+        <v>91977</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>134036163</v>
       </c>
       <c r="B57" t="n">
-        <v>80482</v>
+        <v>80478</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>134040818</v>
       </c>
       <c r="B58" t="n">
-        <v>91943</v>
+        <v>91953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>134036145</v>
       </c>
       <c r="B59" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>134041937</v>
       </c>
       <c r="B60" t="n">
-        <v>91943</v>
+        <v>91953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>134086724</v>
       </c>
       <c r="B61" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 2278-2026 artfynd.xlsx
+++ b/artfynd/A 2278-2026 artfynd.xlsx
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134040810</v>
+        <v>134036167</v>
       </c>
       <c r="B10" t="n">
-        <v>80485</v>
+        <v>96396</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,37 +1586,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594501</v>
+        <v>594607</v>
       </c>
       <c r="R10" t="n">
-        <v>7106169</v>
+        <v>7106088</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,12 +1670,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1686,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134036167</v>
+        <v>134040810</v>
       </c>
       <c r="B11" t="n">
-        <v>96396</v>
+        <v>80485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,37 +1697,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594607</v>
+        <v>594501</v>
       </c>
       <c r="R11" t="n">
-        <v>7106088</v>
+        <v>7106169</v>
       </c>
       <c r="S11" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,12 +1781,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1908,32 +1908,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134040826</v>
+        <v>134040803</v>
       </c>
       <c r="B13" t="n">
-        <v>96396</v>
+        <v>79358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594724</v>
+        <v>594534</v>
       </c>
       <c r="R13" t="n">
-        <v>7106118</v>
+        <v>7105996</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,7 +2019,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134040803</v>
+        <v>134040813</v>
       </c>
       <c r="B14" t="n">
         <v>79358</v>
@@ -2054,13 +2054,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594534</v>
+        <v>594504</v>
       </c>
       <c r="R14" t="n">
-        <v>7105996</v>
+        <v>7106177</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,32 +2130,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134040813</v>
+        <v>134040826</v>
       </c>
       <c r="B15" t="n">
-        <v>79358</v>
+        <v>96396</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594504</v>
+        <v>594724</v>
       </c>
       <c r="R15" t="n">
-        <v>7106177</v>
+        <v>7106118</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3011,10 +3011,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134040814</v>
+        <v>134036154</v>
       </c>
       <c r="B23" t="n">
-        <v>91953</v>
+        <v>91971</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3022,37 +3022,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594524</v>
+        <v>594480</v>
       </c>
       <c r="R23" t="n">
-        <v>7106181</v>
+        <v>7106126</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3106,12 +3106,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3122,10 +3122,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134036154</v>
+        <v>134036169</v>
       </c>
       <c r="B24" t="n">
-        <v>91971</v>
+        <v>91957</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,21 +3133,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3157,13 +3157,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594480</v>
+        <v>594612</v>
       </c>
       <c r="R24" t="n">
-        <v>7106126</v>
+        <v>7106097</v>
       </c>
       <c r="S24" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3233,10 +3233,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134036169</v>
+        <v>134040814</v>
       </c>
       <c r="B25" t="n">
-        <v>91957</v>
+        <v>91953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3244,37 +3244,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594612</v>
+        <v>594524</v>
       </c>
       <c r="R25" t="n">
-        <v>7106097</v>
+        <v>7106181</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3328,12 +3328,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3455,7 +3455,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134040815</v>
+        <v>134036168</v>
       </c>
       <c r="B27" t="n">
         <v>79358</v>
@@ -3486,17 +3486,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594571</v>
+        <v>594610</v>
       </c>
       <c r="R27" t="n">
-        <v>7106182</v>
+        <v>7106086</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3535,7 +3535,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt. Med apotecier</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3550,12 +3555,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3677,7 +3682,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134036168</v>
+        <v>134040815</v>
       </c>
       <c r="B29" t="n">
         <v>79358</v>
@@ -3708,17 +3713,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594610</v>
+        <v>594571</v>
       </c>
       <c r="R29" t="n">
-        <v>7106086</v>
+        <v>7106182</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3747,7 +3752,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3757,12 +3762,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt. Med apotecier</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3777,12 +3777,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -4239,48 +4239,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134040821</v>
+        <v>134036151</v>
       </c>
       <c r="B34" t="n">
-        <v>99200</v>
+        <v>91957</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>594701</v>
+        <v>594482</v>
       </c>
       <c r="R34" t="n">
-        <v>7106149</v>
+        <v>7106077</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4334,12 +4334,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4350,45 +4350,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134040827</v>
+        <v>134036157</v>
       </c>
       <c r="B35" t="n">
-        <v>92228</v>
+        <v>80367</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>594535</v>
+        <v>594474</v>
       </c>
       <c r="R35" t="n">
-        <v>7106124</v>
+        <v>7106125</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4445,12 +4445,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4461,48 +4461,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134036151</v>
+        <v>134040821</v>
       </c>
       <c r="B36" t="n">
-        <v>91957</v>
+        <v>99200</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>594482</v>
+        <v>594701</v>
       </c>
       <c r="R36" t="n">
-        <v>7106077</v>
+        <v>7106149</v>
       </c>
       <c r="S36" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4556,12 +4556,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4572,45 +4572,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134036157</v>
+        <v>134040827</v>
       </c>
       <c r="B37" t="n">
-        <v>80367</v>
+        <v>92228</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>594474</v>
+        <v>594535</v>
       </c>
       <c r="R37" t="n">
-        <v>7106125</v>
+        <v>7106124</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,12 +4667,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4683,48 +4683,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134040825</v>
+        <v>134036165</v>
       </c>
       <c r="B38" t="n">
-        <v>79358</v>
+        <v>80485</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>594826</v>
+        <v>594602</v>
       </c>
       <c r="R38" t="n">
-        <v>7106126</v>
+        <v>7106101</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4778,12 +4778,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4794,48 +4794,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134036165</v>
+        <v>134040825</v>
       </c>
       <c r="B39" t="n">
-        <v>80485</v>
+        <v>79358</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>594602</v>
+        <v>594826</v>
       </c>
       <c r="R39" t="n">
-        <v>7106101</v>
+        <v>7106126</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4889,12 +4889,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4905,10 +4905,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134041932</v>
+        <v>134036173</v>
       </c>
       <c r="B40" t="n">
-        <v>80478</v>
+        <v>99200</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4916,37 +4916,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>594484</v>
+        <v>594691</v>
       </c>
       <c r="R40" t="n">
-        <v>7106025</v>
+        <v>7106160</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5000,12 +5000,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5016,10 +5016,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134036173</v>
+        <v>134040824</v>
       </c>
       <c r="B41" t="n">
-        <v>99200</v>
+        <v>80367</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5027,37 +5027,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>594691</v>
+        <v>594761</v>
       </c>
       <c r="R41" t="n">
-        <v>7106160</v>
+        <v>7106145</v>
       </c>
       <c r="S41" t="n">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5111,12 +5111,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5127,32 +5127,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134040824</v>
+        <v>134040828</v>
       </c>
       <c r="B42" t="n">
-        <v>80367</v>
+        <v>92389</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5162,10 +5162,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>594761</v>
+        <v>594548</v>
       </c>
       <c r="R42" t="n">
-        <v>7106145</v>
+        <v>7106114</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5238,45 +5238,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134040828</v>
+        <v>134041932</v>
       </c>
       <c r="B43" t="n">
-        <v>92389</v>
+        <v>80478</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>594548</v>
+        <v>594484</v>
       </c>
       <c r="R43" t="n">
-        <v>7106114</v>
+        <v>7106025</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5333,12 +5333,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5349,53 +5349,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134036150</v>
+        <v>134041933</v>
       </c>
       <c r="B44" t="n">
-        <v>57975</v>
+        <v>80485</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>594479</v>
+        <v>594496</v>
       </c>
       <c r="R44" t="n">
-        <v>7106056</v>
+        <v>7106047</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5427,7 +5419,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5437,14 +5429,14 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="b">
         <v>0</v>
@@ -5452,12 +5444,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5468,48 +5460,56 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134036146</v>
+        <v>134036150</v>
       </c>
       <c r="B45" t="n">
-        <v>92389</v>
+        <v>57975</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>594500</v>
+        <v>594479</v>
       </c>
       <c r="R45" t="n">
-        <v>7106009</v>
+        <v>7106056</v>
       </c>
       <c r="S45" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5548,14 +5548,14 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG45" t="b">
         <v>0</v>
@@ -5579,32 +5579,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134036177</v>
+        <v>134036146</v>
       </c>
       <c r="B46" t="n">
-        <v>92182</v>
+        <v>92389</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5614,13 +5614,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>594739</v>
+        <v>594500</v>
       </c>
       <c r="R46" t="n">
-        <v>7106142</v>
+        <v>7106009</v>
       </c>
       <c r="S46" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134041933</v>
+        <v>134036177</v>
       </c>
       <c r="B47" t="n">
-        <v>80485</v>
+        <v>92182</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5701,37 +5701,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>594496</v>
+        <v>594739</v>
       </c>
       <c r="R47" t="n">
-        <v>7106047</v>
+        <v>7106142</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5785,12 +5785,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -6134,48 +6134,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134041938</v>
+        <v>134036158</v>
       </c>
       <c r="B51" t="n">
-        <v>91953</v>
+        <v>98049</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>221941</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>594721</v>
+        <v>594476</v>
       </c>
       <c r="R51" t="n">
-        <v>7106166</v>
+        <v>7106135</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6229,12 +6229,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6245,32 +6245,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134036158</v>
+        <v>134036179</v>
       </c>
       <c r="B52" t="n">
-        <v>98049</v>
+        <v>91957</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6280,13 +6280,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>594476</v>
+        <v>594582</v>
       </c>
       <c r="R52" t="n">
-        <v>7106135</v>
+        <v>7106116</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6356,10 +6356,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134036179</v>
+        <v>134036152</v>
       </c>
       <c r="B53" t="n">
-        <v>91957</v>
+        <v>80473</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6367,21 +6367,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6391,13 +6391,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>594582</v>
+        <v>594475</v>
       </c>
       <c r="R53" t="n">
-        <v>7106116</v>
+        <v>7106098</v>
       </c>
       <c r="S53" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6467,10 +6467,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134036152</v>
+        <v>134041938</v>
       </c>
       <c r="B54" t="n">
-        <v>80473</v>
+        <v>91953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6478,34 +6478,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>594475</v>
+        <v>594721</v>
       </c>
       <c r="R54" t="n">
-        <v>7106098</v>
+        <v>7106166</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6562,12 +6562,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6697,10 +6697,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134036175</v>
+        <v>134040818</v>
       </c>
       <c r="B56" t="n">
-        <v>91977</v>
+        <v>91953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6708,33 +6708,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>594758</v>
+        <v>594598</v>
       </c>
       <c r="R56" t="n">
-        <v>7106168</v>
+        <v>7106142</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6763,7 +6767,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6773,7 +6777,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6788,12 +6792,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6915,10 +6919,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134040818</v>
+        <v>134036175</v>
       </c>
       <c r="B58" t="n">
-        <v>91953</v>
+        <v>91977</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6926,37 +6930,33 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>594598</v>
+        <v>594758</v>
       </c>
       <c r="R58" t="n">
-        <v>7106142</v>
+        <v>7106168</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7010,12 +7010,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">

--- a/artfynd/A 2278-2026 artfynd.xlsx
+++ b/artfynd/A 2278-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1908,7 +1908,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134040803</v>
+        <v>134040813</v>
       </c>
       <c r="B13" t="n">
         <v>79358</v>
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594534</v>
+        <v>594504</v>
       </c>
       <c r="R13" t="n">
-        <v>7105996</v>
+        <v>7106177</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,32 +2019,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134040813</v>
+        <v>134040826</v>
       </c>
       <c r="B14" t="n">
-        <v>79358</v>
+        <v>96396</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,13 +2054,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594504</v>
+        <v>594724</v>
       </c>
       <c r="R14" t="n">
-        <v>7106177</v>
+        <v>7106118</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,32 +2130,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134040826</v>
+        <v>134040803</v>
       </c>
       <c r="B15" t="n">
-        <v>96396</v>
+        <v>79358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594724</v>
+        <v>594534</v>
       </c>
       <c r="R15" t="n">
-        <v>7106118</v>
+        <v>7105996</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134041934</v>
+        <v>134036149</v>
       </c>
       <c r="B16" t="n">
-        <v>91977</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,33 +2252,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594559</v>
+        <v>594477</v>
       </c>
       <c r="R16" t="n">
-        <v>7106144</v>
+        <v>7106037</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2307,7 +2311,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2317,7 +2321,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2332,12 +2336,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2348,10 +2352,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134036149</v>
+        <v>134041934</v>
       </c>
       <c r="B17" t="n">
-        <v>57972</v>
+        <v>91977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,37 +2363,33 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594477</v>
+        <v>594559</v>
       </c>
       <c r="R17" t="n">
-        <v>7106037</v>
+        <v>7106144</v>
       </c>
       <c r="S17" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2443,12 +2443,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2459,10 +2459,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134036160</v>
+        <v>134040808</v>
       </c>
       <c r="B18" t="n">
-        <v>96396</v>
+        <v>80485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2470,37 +2470,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2809</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594497</v>
+        <v>594483</v>
       </c>
       <c r="R18" t="n">
-        <v>7106164</v>
+        <v>7106035</v>
       </c>
       <c r="S18" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2554,12 +2554,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2570,30 +2570,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134036159</v>
+        <v>134036160</v>
       </c>
       <c r="B19" t="n">
-        <v>91977</v>
+        <v>96396</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2601,13 +2605,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594504</v>
+        <v>594497</v>
       </c>
       <c r="R19" t="n">
-        <v>7106148</v>
+        <v>7106164</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2636,7 +2640,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2646,7 +2650,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2677,34 +2681,30 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134036172</v>
+        <v>134036159</v>
       </c>
       <c r="B20" t="n">
-        <v>80367</v>
+        <v>91977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2712,13 +2712,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594619</v>
+        <v>594504</v>
       </c>
       <c r="R20" t="n">
-        <v>7106110</v>
+        <v>7106148</v>
       </c>
       <c r="S20" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2766,7 +2766,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2789,48 +2788,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134040806</v>
+        <v>134036172</v>
       </c>
       <c r="B21" t="n">
-        <v>91953</v>
+        <v>80367</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594500</v>
+        <v>594619</v>
       </c>
       <c r="R21" t="n">
-        <v>7106023</v>
+        <v>7106110</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2859,7 +2858,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2869,7 +2868,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2878,18 +2877,19 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2900,32 +2900,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134040808</v>
+        <v>134040806</v>
       </c>
       <c r="B22" t="n">
-        <v>80485</v>
+        <v>91953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2935,10 +2935,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594483</v>
+        <v>594500</v>
       </c>
       <c r="R22" t="n">
-        <v>7106035</v>
+        <v>7106023</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3011,32 +3011,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134036154</v>
+        <v>134036155</v>
       </c>
       <c r="B23" t="n">
-        <v>91971</v>
+        <v>80423</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3046,13 +3046,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594480</v>
+        <v>594466</v>
       </c>
       <c r="R23" t="n">
-        <v>7106126</v>
+        <v>7106117</v>
       </c>
       <c r="S23" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3122,10 +3122,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134036169</v>
+        <v>134036154</v>
       </c>
       <c r="B24" t="n">
-        <v>91957</v>
+        <v>91971</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,21 +3133,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3157,13 +3157,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594612</v>
+        <v>594480</v>
       </c>
       <c r="R24" t="n">
-        <v>7106097</v>
+        <v>7106126</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3233,10 +3233,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134040814</v>
+        <v>134036169</v>
       </c>
       <c r="B25" t="n">
-        <v>91953</v>
+        <v>91957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3244,37 +3244,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594524</v>
+        <v>594612</v>
       </c>
       <c r="R25" t="n">
-        <v>7106181</v>
+        <v>7106097</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3328,12 +3328,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3344,45 +3344,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134036155</v>
+        <v>134040814</v>
       </c>
       <c r="B26" t="n">
-        <v>80423</v>
+        <v>91953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594466</v>
+        <v>594524</v>
       </c>
       <c r="R26" t="n">
-        <v>7106117</v>
+        <v>7106181</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3439,12 +3439,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3571,7 +3571,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134040807</v>
+        <v>134040815</v>
       </c>
       <c r="B28" t="n">
         <v>79358</v>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594496</v>
+        <v>594571</v>
       </c>
       <c r="R28" t="n">
-        <v>7106021</v>
+        <v>7106182</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3682,7 +3682,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134040815</v>
+        <v>134040807</v>
       </c>
       <c r="B29" t="n">
         <v>79358</v>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594571</v>
+        <v>594496</v>
       </c>
       <c r="R29" t="n">
-        <v>7106182</v>
+        <v>7106021</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4239,10 +4239,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134036151</v>
+        <v>134040827</v>
       </c>
       <c r="B34" t="n">
-        <v>91957</v>
+        <v>92228</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4250,37 +4250,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>594482</v>
+        <v>594535</v>
       </c>
       <c r="R34" t="n">
-        <v>7106077</v>
+        <v>7106124</v>
       </c>
       <c r="S34" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4334,12 +4334,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4350,10 +4350,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134036157</v>
+        <v>134040821</v>
       </c>
       <c r="B35" t="n">
-        <v>80367</v>
+        <v>99200</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4361,34 +4361,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>594474</v>
+        <v>594701</v>
       </c>
       <c r="R35" t="n">
-        <v>7106125</v>
+        <v>7106149</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4445,12 +4445,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4461,48 +4461,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134040821</v>
+        <v>134036151</v>
       </c>
       <c r="B36" t="n">
-        <v>99200</v>
+        <v>91957</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>594701</v>
+        <v>594482</v>
       </c>
       <c r="R36" t="n">
-        <v>7106149</v>
+        <v>7106077</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4556,12 +4556,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4572,45 +4572,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134040827</v>
+        <v>134036157</v>
       </c>
       <c r="B37" t="n">
-        <v>92228</v>
+        <v>80367</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>594535</v>
+        <v>594474</v>
       </c>
       <c r="R37" t="n">
-        <v>7106124</v>
+        <v>7106125</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,12 +4667,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4905,10 +4905,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134036173</v>
+        <v>134041932</v>
       </c>
       <c r="B40" t="n">
-        <v>99200</v>
+        <v>80478</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4916,37 +4916,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>594691</v>
+        <v>594484</v>
       </c>
       <c r="R40" t="n">
-        <v>7106160</v>
+        <v>7106025</v>
       </c>
       <c r="S40" t="n">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5000,12 +5000,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5016,10 +5016,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134040824</v>
+        <v>134036173</v>
       </c>
       <c r="B41" t="n">
-        <v>80367</v>
+        <v>99200</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5027,37 +5027,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>594761</v>
+        <v>594691</v>
       </c>
       <c r="R41" t="n">
-        <v>7106145</v>
+        <v>7106160</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5111,12 +5111,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5238,10 +5238,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134041932</v>
+        <v>134040824</v>
       </c>
       <c r="B43" t="n">
-        <v>80478</v>
+        <v>80367</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5249,34 +5249,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>594484</v>
+        <v>594761</v>
       </c>
       <c r="R43" t="n">
-        <v>7106025</v>
+        <v>7106145</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5333,12 +5333,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5349,45 +5349,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134041933</v>
+        <v>134036150</v>
       </c>
       <c r="B44" t="n">
-        <v>80485</v>
+        <v>57975</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>594496</v>
+        <v>594479</v>
       </c>
       <c r="R44" t="n">
-        <v>7106047</v>
+        <v>7106056</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5419,7 +5427,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5429,14 +5437,14 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG44" t="b">
         <v>0</v>
@@ -5444,12 +5452,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5460,56 +5468,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134036150</v>
+        <v>134036146</v>
       </c>
       <c r="B45" t="n">
-        <v>57975</v>
+        <v>92389</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>594479</v>
+        <v>594500</v>
       </c>
       <c r="R45" t="n">
-        <v>7106056</v>
+        <v>7106009</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5548,14 +5548,14 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="b">
         <v>0</v>
@@ -5579,32 +5579,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134036146</v>
+        <v>134036177</v>
       </c>
       <c r="B46" t="n">
-        <v>92389</v>
+        <v>92182</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5614,13 +5614,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>594500</v>
+        <v>594739</v>
       </c>
       <c r="R46" t="n">
-        <v>7106009</v>
+        <v>7106142</v>
       </c>
       <c r="S46" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134036177</v>
+        <v>134041933</v>
       </c>
       <c r="B47" t="n">
-        <v>92182</v>
+        <v>80485</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5701,37 +5701,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>594739</v>
+        <v>594496</v>
       </c>
       <c r="R47" t="n">
-        <v>7106142</v>
+        <v>7106047</v>
       </c>
       <c r="S47" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5785,12 +5785,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -6356,10 +6356,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134036152</v>
+        <v>134041938</v>
       </c>
       <c r="B53" t="n">
-        <v>80473</v>
+        <v>91953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6367,34 +6367,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>594475</v>
+        <v>594721</v>
       </c>
       <c r="R53" t="n">
-        <v>7106098</v>
+        <v>7106166</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6451,12 +6451,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6467,10 +6467,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134041938</v>
+        <v>134036152</v>
       </c>
       <c r="B54" t="n">
-        <v>91953</v>
+        <v>80473</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6478,34 +6478,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>594721</v>
+        <v>594475</v>
       </c>
       <c r="R54" t="n">
-        <v>7106166</v>
+        <v>7106098</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6562,12 +6562,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6808,34 +6808,30 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134036163</v>
+        <v>134036175</v>
       </c>
       <c r="B57" t="n">
-        <v>80478</v>
+        <v>91977</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6843,13 +6839,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>594604</v>
+        <v>594758</v>
       </c>
       <c r="R57" t="n">
-        <v>7106104</v>
+        <v>7106168</v>
       </c>
       <c r="S57" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6878,7 +6874,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6888,7 +6884,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6919,30 +6915,34 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134036175</v>
+        <v>134036163</v>
       </c>
       <c r="B58" t="n">
-        <v>91977</v>
+        <v>80478</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6950,13 +6950,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>594758</v>
+        <v>594604</v>
       </c>
       <c r="R58" t="n">
-        <v>7106168</v>
+        <v>7106104</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7026,10 +7026,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134036145</v>
+        <v>134041937</v>
       </c>
       <c r="B59" t="n">
-        <v>91957</v>
+        <v>91953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7037,37 +7037,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>594513</v>
+        <v>594714</v>
       </c>
       <c r="R59" t="n">
-        <v>7106004</v>
+        <v>7106130</v>
       </c>
       <c r="S59" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7121,12 +7121,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7137,10 +7137,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134041937</v>
+        <v>134036145</v>
       </c>
       <c r="B60" t="n">
-        <v>91953</v>
+        <v>91957</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7148,37 +7148,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>594714</v>
+        <v>594513</v>
       </c>
       <c r="R60" t="n">
-        <v>7106130</v>
+        <v>7106004</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7232,12 +7232,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7366,6 +7366,117 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>134040812</v>
+      </c>
+      <c r="B62" t="n">
+        <v>83348</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>594508</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7106172</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2278-2026 artfynd.xlsx
+++ b/artfynd/A 2278-2026 artfynd.xlsx
@@ -3455,7 +3455,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134036168</v>
+        <v>134040815</v>
       </c>
       <c r="B27" t="n">
         <v>79358</v>
@@ -3486,17 +3486,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594610</v>
+        <v>594571</v>
       </c>
       <c r="R27" t="n">
-        <v>7106086</v>
+        <v>7106182</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3535,12 +3535,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt. Med apotecier</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3555,12 +3550,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3571,7 +3566,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134040815</v>
+        <v>134040807</v>
       </c>
       <c r="B28" t="n">
         <v>79358</v>
@@ -3606,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594571</v>
+        <v>594496</v>
       </c>
       <c r="R28" t="n">
-        <v>7106182</v>
+        <v>7106021</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3641,7 +3636,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3651,7 +3646,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3682,7 +3677,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134040807</v>
+        <v>134036168</v>
       </c>
       <c r="B29" t="n">
         <v>79358</v>
@@ -3713,17 +3708,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594496</v>
+        <v>594610</v>
       </c>
       <c r="R29" t="n">
-        <v>7106021</v>
+        <v>7106086</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3752,7 +3747,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3762,7 +3757,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt. Med apotecier</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3777,12 +3777,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -6697,10 +6697,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134040818</v>
+        <v>134036175</v>
       </c>
       <c r="B56" t="n">
-        <v>91953</v>
+        <v>91977</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6708,37 +6708,33 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>594598</v>
+        <v>594758</v>
       </c>
       <c r="R56" t="n">
-        <v>7106142</v>
+        <v>7106168</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6767,7 +6763,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6777,7 +6773,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6792,12 +6788,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6808,30 +6804,34 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134036175</v>
+        <v>134036163</v>
       </c>
       <c r="B57" t="n">
-        <v>91977</v>
+        <v>80478</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6839,13 +6839,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>594758</v>
+        <v>594604</v>
       </c>
       <c r="R57" t="n">
-        <v>7106168</v>
+        <v>7106104</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6915,48 +6915,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134036163</v>
+        <v>134040818</v>
       </c>
       <c r="B58" t="n">
-        <v>80478</v>
+        <v>91953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>594604</v>
+        <v>594598</v>
       </c>
       <c r="R58" t="n">
-        <v>7106104</v>
+        <v>7106142</v>
       </c>
       <c r="S58" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7010,12 +7010,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7026,10 +7026,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134041937</v>
+        <v>134036145</v>
       </c>
       <c r="B59" t="n">
-        <v>91953</v>
+        <v>91957</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7037,37 +7037,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>594714</v>
+        <v>594513</v>
       </c>
       <c r="R59" t="n">
-        <v>7106130</v>
+        <v>7106004</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7121,12 +7121,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7137,10 +7137,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134036145</v>
+        <v>134041937</v>
       </c>
       <c r="B60" t="n">
-        <v>91957</v>
+        <v>91953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7148,37 +7148,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>594513</v>
+        <v>594714</v>
       </c>
       <c r="R60" t="n">
-        <v>7106004</v>
+        <v>7106130</v>
       </c>
       <c r="S60" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7232,12 +7232,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">

--- a/artfynd/A 2278-2026 artfynd.xlsx
+++ b/artfynd/A 2278-2026 artfynd.xlsx
@@ -2459,10 +2459,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134040808</v>
+        <v>134036160</v>
       </c>
       <c r="B18" t="n">
-        <v>80485</v>
+        <v>96396</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2470,37 +2470,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>2809</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594483</v>
+        <v>594497</v>
       </c>
       <c r="R18" t="n">
-        <v>7106035</v>
+        <v>7106164</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2554,12 +2554,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2570,34 +2570,30 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134036160</v>
+        <v>134036159</v>
       </c>
       <c r="B19" t="n">
-        <v>96396</v>
+        <v>91977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2605,13 +2601,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594497</v>
+        <v>594504</v>
       </c>
       <c r="R19" t="n">
-        <v>7106164</v>
+        <v>7106148</v>
       </c>
       <c r="S19" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2640,7 +2636,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2650,7 +2646,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2681,30 +2677,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134036159</v>
+        <v>134036172</v>
       </c>
       <c r="B20" t="n">
-        <v>91977</v>
+        <v>80367</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2712,13 +2712,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594504</v>
+        <v>594619</v>
       </c>
       <c r="R20" t="n">
-        <v>7106148</v>
+        <v>7106110</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2766,6 +2766,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2788,10 +2789,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134036172</v>
+        <v>134040808</v>
       </c>
       <c r="B21" t="n">
-        <v>80367</v>
+        <v>80485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2799,37 +2800,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594619</v>
+        <v>594483</v>
       </c>
       <c r="R21" t="n">
-        <v>7106110</v>
+        <v>7106035</v>
       </c>
       <c r="S21" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2858,7 +2859,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2868,7 +2869,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2877,19 +2878,18 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">

--- a/artfynd/A 2278-2026 artfynd.xlsx
+++ b/artfynd/A 2278-2026 artfynd.xlsx
@@ -2459,10 +2459,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134036160</v>
+        <v>134040808</v>
       </c>
       <c r="B18" t="n">
-        <v>96396</v>
+        <v>80485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2470,37 +2470,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2809</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594497</v>
+        <v>594483</v>
       </c>
       <c r="R18" t="n">
-        <v>7106164</v>
+        <v>7106035</v>
       </c>
       <c r="S18" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2554,12 +2554,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2570,30 +2570,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134036159</v>
+        <v>134036160</v>
       </c>
       <c r="B19" t="n">
-        <v>91977</v>
+        <v>96396</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2601,13 +2605,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594504</v>
+        <v>594497</v>
       </c>
       <c r="R19" t="n">
-        <v>7106148</v>
+        <v>7106164</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2636,7 +2640,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2646,7 +2650,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2677,34 +2681,30 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134036172</v>
+        <v>134036159</v>
       </c>
       <c r="B20" t="n">
-        <v>80367</v>
+        <v>91977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2712,13 +2712,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594619</v>
+        <v>594504</v>
       </c>
       <c r="R20" t="n">
-        <v>7106110</v>
+        <v>7106148</v>
       </c>
       <c r="S20" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2766,7 +2766,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2789,10 +2788,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134040808</v>
+        <v>134036172</v>
       </c>
       <c r="B21" t="n">
-        <v>80485</v>
+        <v>80367</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2800,37 +2799,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594483</v>
+        <v>594619</v>
       </c>
       <c r="R21" t="n">
-        <v>7106035</v>
+        <v>7106110</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2859,7 +2858,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2869,7 +2868,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2878,18 +2877,19 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -4239,10 +4239,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134040827</v>
+        <v>134036151</v>
       </c>
       <c r="B34" t="n">
-        <v>92228</v>
+        <v>91957</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4250,37 +4250,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>594535</v>
+        <v>594482</v>
       </c>
       <c r="R34" t="n">
-        <v>7106124</v>
+        <v>7106077</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4334,12 +4334,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4350,10 +4350,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134040821</v>
+        <v>134036157</v>
       </c>
       <c r="B35" t="n">
-        <v>99200</v>
+        <v>80367</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4361,34 +4361,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>594701</v>
+        <v>594474</v>
       </c>
       <c r="R35" t="n">
-        <v>7106149</v>
+        <v>7106125</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4445,12 +4445,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4461,10 +4461,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134036151</v>
+        <v>134040827</v>
       </c>
       <c r="B36" t="n">
-        <v>91957</v>
+        <v>92228</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4472,37 +4472,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>594482</v>
+        <v>594535</v>
       </c>
       <c r="R36" t="n">
-        <v>7106077</v>
+        <v>7106124</v>
       </c>
       <c r="S36" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4556,12 +4556,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4572,10 +4572,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134036157</v>
+        <v>134040821</v>
       </c>
       <c r="B37" t="n">
-        <v>80367</v>
+        <v>99200</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4583,34 +4583,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6456</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>594474</v>
+        <v>594701</v>
       </c>
       <c r="R37" t="n">
-        <v>7106125</v>
+        <v>7106149</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,12 +4667,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">

--- a/artfynd/A 2278-2026 artfynd.xlsx
+++ b/artfynd/A 2278-2026 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134004112</v>
+        <v>134004110</v>
       </c>
       <c r="B3" t="n">
-        <v>80478</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594779</v>
+        <v>594497</v>
       </c>
       <c r="R3" t="n">
-        <v>7106096</v>
+        <v>7106185</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,32 +903,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134004110</v>
+        <v>134004112</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>80479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,13 +938,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594497</v>
+        <v>594779</v>
       </c>
       <c r="R4" t="n">
-        <v>7106185</v>
+        <v>7106096</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,12 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,7 +1017,7 @@
         <v>134004114</v>
       </c>
       <c r="B5" t="n">
-        <v>92228</v>
+        <v>92230</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134005846</v>
+        <v>134004111</v>
       </c>
       <c r="B8" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,17 +1388,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>a 2278-2026, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594599</v>
+        <v>594815</v>
       </c>
       <c r="R8" t="n">
-        <v>7106170</v>
+        <v>7106147</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,22 +1452,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134004111</v>
+        <v>134005846</v>
       </c>
       <c r="B9" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,17 +1499,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>a 2278-2026, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594815</v>
+        <v>594599</v>
       </c>
       <c r="R9" t="n">
-        <v>7106147</v>
+        <v>7106170</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,26 +1563,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Patrik Eriksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>134036167</v>
       </c>
       <c r="B10" t="n">
-        <v>96396</v>
+        <v>96398</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>134040810</v>
       </c>
       <c r="B11" t="n">
-        <v>80485</v>
+        <v>80486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>134040804</v>
       </c>
       <c r="B12" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,32 +1908,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134040813</v>
+        <v>134040826</v>
       </c>
       <c r="B13" t="n">
-        <v>79358</v>
+        <v>96398</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594504</v>
+        <v>594724</v>
       </c>
       <c r="R13" t="n">
-        <v>7106177</v>
+        <v>7106118</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,32 +2019,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134040826</v>
+        <v>134040803</v>
       </c>
       <c r="B14" t="n">
-        <v>96396</v>
+        <v>79359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,13 +2054,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594724</v>
+        <v>594534</v>
       </c>
       <c r="R14" t="n">
-        <v>7106118</v>
+        <v>7105996</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134040803</v>
+        <v>134040813</v>
       </c>
       <c r="B15" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594534</v>
+        <v>594504</v>
       </c>
       <c r="R15" t="n">
-        <v>7105996</v>
+        <v>7106177</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134036149</v>
+        <v>134041934</v>
       </c>
       <c r="B16" t="n">
-        <v>57972</v>
+        <v>91979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,37 +2252,33 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594477</v>
+        <v>594559</v>
       </c>
       <c r="R16" t="n">
-        <v>7106037</v>
+        <v>7106144</v>
       </c>
       <c r="S16" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2311,7 +2307,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2321,7 +2317,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,12 +2332,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2352,10 +2348,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134041934</v>
+        <v>134036149</v>
       </c>
       <c r="B17" t="n">
-        <v>91977</v>
+        <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2363,33 +2359,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594559</v>
+        <v>594477</v>
       </c>
       <c r="R17" t="n">
-        <v>7106144</v>
+        <v>7106037</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2443,12 +2443,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2462,7 +2462,7 @@
         <v>134040808</v>
       </c>
       <c r="B18" t="n">
-        <v>80485</v>
+        <v>80486</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,48 +2570,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134036160</v>
+        <v>134040806</v>
       </c>
       <c r="B19" t="n">
-        <v>96396</v>
+        <v>91955</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594497</v>
+        <v>594500</v>
       </c>
       <c r="R19" t="n">
-        <v>7106164</v>
+        <v>7106023</v>
       </c>
       <c r="S19" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,12 +2665,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2681,30 +2681,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134036159</v>
+        <v>134036160</v>
       </c>
       <c r="B20" t="n">
-        <v>91977</v>
+        <v>96398</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2712,13 +2716,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594504</v>
+        <v>594497</v>
       </c>
       <c r="R20" t="n">
-        <v>7106148</v>
+        <v>7106164</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2747,7 +2751,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2757,7 +2761,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2788,34 +2792,30 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134036172</v>
+        <v>134036159</v>
       </c>
       <c r="B21" t="n">
-        <v>80367</v>
+        <v>91979</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2823,13 +2823,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594619</v>
+        <v>594504</v>
       </c>
       <c r="R21" t="n">
-        <v>7106110</v>
+        <v>7106148</v>
       </c>
       <c r="S21" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2877,7 +2877,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2900,48 +2899,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134040806</v>
+        <v>134036172</v>
       </c>
       <c r="B22" t="n">
-        <v>91953</v>
+        <v>80368</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594500</v>
+        <v>594619</v>
       </c>
       <c r="R22" t="n">
-        <v>7106023</v>
+        <v>7106110</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2970,7 +2969,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2980,7 +2979,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,18 +2988,19 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3011,32 +3011,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134036155</v>
+        <v>134036154</v>
       </c>
       <c r="B23" t="n">
-        <v>80423</v>
+        <v>91973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3046,13 +3046,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594466</v>
+        <v>594480</v>
       </c>
       <c r="R23" t="n">
-        <v>7106117</v>
+        <v>7106126</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3122,10 +3122,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134036154</v>
+        <v>134036169</v>
       </c>
       <c r="B24" t="n">
-        <v>91971</v>
+        <v>91959</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,21 +3133,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3157,13 +3157,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594480</v>
+        <v>594612</v>
       </c>
       <c r="R24" t="n">
-        <v>7106126</v>
+        <v>7106097</v>
       </c>
       <c r="S24" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3233,32 +3233,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134036169</v>
+        <v>134036155</v>
       </c>
       <c r="B25" t="n">
-        <v>91957</v>
+        <v>80424</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3268,13 +3268,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594612</v>
+        <v>594466</v>
       </c>
       <c r="R25" t="n">
-        <v>7106097</v>
+        <v>7106117</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,7 +3347,7 @@
         <v>134040814</v>
       </c>
       <c r="B26" t="n">
-        <v>91953</v>
+        <v>91955</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134040815</v>
+        <v>134036168</v>
       </c>
       <c r="B27" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3486,17 +3486,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594571</v>
+        <v>594610</v>
       </c>
       <c r="R27" t="n">
-        <v>7106182</v>
+        <v>7106086</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3535,7 +3535,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt. Med apotecier</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3550,12 +3555,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3566,10 +3571,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134040807</v>
+        <v>134040815</v>
       </c>
       <c r="B28" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3601,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594496</v>
+        <v>594571</v>
       </c>
       <c r="R28" t="n">
-        <v>7106021</v>
+        <v>7106182</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3636,7 +3641,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3646,7 +3651,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3677,10 +3682,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134036168</v>
+        <v>134040807</v>
       </c>
       <c r="B29" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3708,17 +3713,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594610</v>
+        <v>594496</v>
       </c>
       <c r="R29" t="n">
-        <v>7106086</v>
+        <v>7106021</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3747,7 +3752,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3757,12 +3762,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt. Med apotecier</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3777,12 +3777,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3796,7 +3796,7 @@
         <v>134036147</v>
       </c>
       <c r="B30" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>134040822</v>
       </c>
       <c r="B31" t="n">
-        <v>99200</v>
+        <v>99202</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>134036161</v>
       </c>
       <c r="B32" t="n">
-        <v>80367</v>
+        <v>80368</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>134040805</v>
       </c>
       <c r="B33" t="n">
-        <v>80485</v>
+        <v>80486</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4239,48 +4239,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134036151</v>
+        <v>134040821</v>
       </c>
       <c r="B34" t="n">
-        <v>91957</v>
+        <v>99202</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>594482</v>
+        <v>594701</v>
       </c>
       <c r="R34" t="n">
-        <v>7106077</v>
+        <v>7106149</v>
       </c>
       <c r="S34" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4334,12 +4334,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4350,45 +4350,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134036157</v>
+        <v>134040827</v>
       </c>
       <c r="B35" t="n">
-        <v>80367</v>
+        <v>92230</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>594474</v>
+        <v>594535</v>
       </c>
       <c r="R35" t="n">
-        <v>7106125</v>
+        <v>7106124</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4445,12 +4445,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4461,10 +4461,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134040827</v>
+        <v>134036151</v>
       </c>
       <c r="B36" t="n">
-        <v>92228</v>
+        <v>91959</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4472,37 +4472,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>594535</v>
+        <v>594482</v>
       </c>
       <c r="R36" t="n">
-        <v>7106124</v>
+        <v>7106077</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4556,12 +4556,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4572,10 +4572,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134040821</v>
+        <v>134036157</v>
       </c>
       <c r="B37" t="n">
-        <v>99200</v>
+        <v>80368</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4583,34 +4583,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>6456</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>594701</v>
+        <v>594474</v>
       </c>
       <c r="R37" t="n">
-        <v>7106149</v>
+        <v>7106125</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,12 +4667,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4683,48 +4683,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134036165</v>
+        <v>134040825</v>
       </c>
       <c r="B38" t="n">
-        <v>80485</v>
+        <v>79359</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>594602</v>
+        <v>594826</v>
       </c>
       <c r="R38" t="n">
-        <v>7106101</v>
+        <v>7106126</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4778,12 +4778,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4794,48 +4794,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134040825</v>
+        <v>134036165</v>
       </c>
       <c r="B39" t="n">
-        <v>79358</v>
+        <v>80486</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>594826</v>
+        <v>594602</v>
       </c>
       <c r="R39" t="n">
-        <v>7106126</v>
+        <v>7106101</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4889,12 +4889,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4905,10 +4905,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134041932</v>
+        <v>134036173</v>
       </c>
       <c r="B40" t="n">
-        <v>80478</v>
+        <v>99202</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4916,37 +4916,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>594484</v>
+        <v>594691</v>
       </c>
       <c r="R40" t="n">
-        <v>7106025</v>
+        <v>7106160</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5000,12 +5000,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5016,48 +5016,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134036173</v>
+        <v>134040828</v>
       </c>
       <c r="B41" t="n">
-        <v>99200</v>
+        <v>92391</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>594691</v>
+        <v>594548</v>
       </c>
       <c r="R41" t="n">
-        <v>7106160</v>
+        <v>7106114</v>
       </c>
       <c r="S41" t="n">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5111,12 +5111,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5127,32 +5127,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134040828</v>
+        <v>134040824</v>
       </c>
       <c r="B42" t="n">
-        <v>92389</v>
+        <v>80368</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5162,10 +5162,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>594548</v>
+        <v>594761</v>
       </c>
       <c r="R42" t="n">
-        <v>7106114</v>
+        <v>7106145</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5238,10 +5238,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134040824</v>
+        <v>134041932</v>
       </c>
       <c r="B43" t="n">
-        <v>80367</v>
+        <v>80479</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5249,34 +5249,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>594761</v>
+        <v>594484</v>
       </c>
       <c r="R43" t="n">
-        <v>7106145</v>
+        <v>7106025</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5333,12 +5333,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5349,56 +5349,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134036150</v>
+        <v>134036146</v>
       </c>
       <c r="B44" t="n">
-        <v>57975</v>
+        <v>92391</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>594479</v>
+        <v>594500</v>
       </c>
       <c r="R44" t="n">
-        <v>7106056</v>
+        <v>7106009</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5427,7 +5419,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5437,14 +5429,14 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="b">
         <v>0</v>
@@ -5468,48 +5460,56 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134036146</v>
+        <v>134036150</v>
       </c>
       <c r="B45" t="n">
-        <v>92389</v>
+        <v>57975</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>594500</v>
+        <v>594479</v>
       </c>
       <c r="R45" t="n">
-        <v>7106009</v>
+        <v>7106056</v>
       </c>
       <c r="S45" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5548,14 +5548,14 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG45" t="b">
         <v>0</v>
@@ -5582,7 +5582,7 @@
         <v>134036177</v>
       </c>
       <c r="B46" t="n">
-        <v>92182</v>
+        <v>92184</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>134041933</v>
       </c>
       <c r="B47" t="n">
-        <v>80485</v>
+        <v>80486</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5801,32 +5801,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134036170</v>
+        <v>134036171</v>
       </c>
       <c r="B48" t="n">
-        <v>92672</v>
+        <v>91973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>898</v>
+        <v>1204</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5839,10 +5839,10 @@
         <v>594612</v>
       </c>
       <c r="R48" t="n">
-        <v>7106097</v>
+        <v>7106094</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5912,32 +5912,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134036171</v>
+        <v>134036170</v>
       </c>
       <c r="B49" t="n">
-        <v>91971</v>
+        <v>92674</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1204</v>
+        <v>898</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5950,10 +5950,10 @@
         <v>594612</v>
       </c>
       <c r="R49" t="n">
-        <v>7106094</v>
+        <v>7106097</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6026,7 +6026,7 @@
         <v>134040809</v>
       </c>
       <c r="B50" t="n">
-        <v>91971</v>
+        <v>91973</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>134036158</v>
       </c>
       <c r="B51" t="n">
-        <v>98049</v>
+        <v>98051</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6245,10 +6245,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134036179</v>
+        <v>134036152</v>
       </c>
       <c r="B52" t="n">
-        <v>91957</v>
+        <v>80474</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6256,21 +6256,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6280,13 +6280,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>594582</v>
+        <v>594475</v>
       </c>
       <c r="R52" t="n">
-        <v>7106116</v>
+        <v>7106098</v>
       </c>
       <c r="S52" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6356,10 +6356,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134041938</v>
+        <v>134036179</v>
       </c>
       <c r="B53" t="n">
-        <v>91953</v>
+        <v>91959</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6367,37 +6367,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>594721</v>
+        <v>594582</v>
       </c>
       <c r="R53" t="n">
-        <v>7106166</v>
+        <v>7106116</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6451,12 +6451,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6467,10 +6467,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134036152</v>
+        <v>134041938</v>
       </c>
       <c r="B54" t="n">
-        <v>80473</v>
+        <v>91955</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6478,34 +6478,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>594475</v>
+        <v>594721</v>
       </c>
       <c r="R54" t="n">
-        <v>7106098</v>
+        <v>7106166</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6562,12 +6562,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6581,7 +6581,7 @@
         <v>134040817</v>
       </c>
       <c r="B55" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>134036175</v>
       </c>
       <c r="B56" t="n">
-        <v>91977</v>
+        <v>91979</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>134036163</v>
       </c>
       <c r="B57" t="n">
-        <v>80478</v>
+        <v>80479</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>134040818</v>
       </c>
       <c r="B58" t="n">
-        <v>91953</v>
+        <v>91955</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>134036145</v>
       </c>
       <c r="B59" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>134041937</v>
       </c>
       <c r="B60" t="n">
-        <v>91953</v>
+        <v>91955</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>134086724</v>
       </c>
       <c r="B61" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>134040812</v>
       </c>
       <c r="B62" t="n">
-        <v>83348</v>
+        <v>83349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 2278-2026 artfynd.xlsx
+++ b/artfynd/A 2278-2026 artfynd.xlsx
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134036167</v>
+        <v>134040810</v>
       </c>
       <c r="B10" t="n">
-        <v>96398</v>
+        <v>80486</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,37 +1586,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594607</v>
+        <v>594501</v>
       </c>
       <c r="R10" t="n">
-        <v>7106088</v>
+        <v>7106169</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,12 +1670,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1686,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134040810</v>
+        <v>134036167</v>
       </c>
       <c r="B11" t="n">
-        <v>80486</v>
+        <v>96398</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,37 +1697,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594501</v>
+        <v>594607</v>
       </c>
       <c r="R11" t="n">
-        <v>7106169</v>
+        <v>7106088</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,12 +1781,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2459,10 +2459,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134040808</v>
+        <v>134036160</v>
       </c>
       <c r="B18" t="n">
-        <v>80486</v>
+        <v>96398</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2470,37 +2470,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>2809</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594483</v>
+        <v>594497</v>
       </c>
       <c r="R18" t="n">
-        <v>7106035</v>
+        <v>7106164</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2554,12 +2554,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2570,10 +2570,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134040806</v>
+        <v>134036159</v>
       </c>
       <c r="B19" t="n">
-        <v>91955</v>
+        <v>91979</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2581,34 +2581,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594500</v>
+        <v>594504</v>
       </c>
       <c r="R19" t="n">
-        <v>7106023</v>
+        <v>7106148</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2640,7 +2636,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2650,7 +2646,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,12 +2661,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2681,10 +2677,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134036160</v>
+        <v>134036172</v>
       </c>
       <c r="B20" t="n">
-        <v>96398</v>
+        <v>80368</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2692,21 +2688,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2809</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2716,13 +2712,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594497</v>
+        <v>594619</v>
       </c>
       <c r="R20" t="n">
-        <v>7106164</v>
+        <v>7106110</v>
       </c>
       <c r="S20" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2751,7 +2747,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2761,7 +2757,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,6 +2766,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2792,10 +2789,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134036159</v>
+        <v>134040806</v>
       </c>
       <c r="B21" t="n">
-        <v>91979</v>
+        <v>91955</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,30 +2800,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594504</v>
+        <v>594500</v>
       </c>
       <c r="R21" t="n">
-        <v>7106148</v>
+        <v>7106023</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2858,7 +2859,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2868,7 +2869,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2883,12 +2884,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2899,10 +2900,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134036172</v>
+        <v>134040808</v>
       </c>
       <c r="B22" t="n">
-        <v>80368</v>
+        <v>80486</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,37 +2911,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594619</v>
+        <v>594483</v>
       </c>
       <c r="R22" t="n">
-        <v>7106110</v>
+        <v>7106035</v>
       </c>
       <c r="S22" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2969,7 +2970,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2979,7 +2980,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2988,19 +2989,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3455,7 +3455,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134036168</v>
+        <v>134040815</v>
       </c>
       <c r="B27" t="n">
         <v>79359</v>
@@ -3486,17 +3486,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594610</v>
+        <v>594571</v>
       </c>
       <c r="R27" t="n">
-        <v>7106086</v>
+        <v>7106182</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3535,12 +3535,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt. Med apotecier</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3555,12 +3550,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3571,7 +3566,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134040815</v>
+        <v>134040807</v>
       </c>
       <c r="B28" t="n">
         <v>79359</v>
@@ -3606,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594571</v>
+        <v>594496</v>
       </c>
       <c r="R28" t="n">
-        <v>7106182</v>
+        <v>7106021</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3641,7 +3636,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3651,7 +3646,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3682,7 +3677,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134040807</v>
+        <v>134036168</v>
       </c>
       <c r="B29" t="n">
         <v>79359</v>
@@ -3713,17 +3708,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594496</v>
+        <v>594610</v>
       </c>
       <c r="R29" t="n">
-        <v>7106021</v>
+        <v>7106086</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3752,7 +3747,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3762,7 +3757,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt. Med apotecier</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3777,12 +3777,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3793,48 +3793,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134036147</v>
+        <v>134040822</v>
       </c>
       <c r="B30" t="n">
-        <v>80474</v>
+        <v>99202</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>594500</v>
+        <v>594708</v>
       </c>
       <c r="R30" t="n">
-        <v>7106009</v>
+        <v>7106124</v>
       </c>
       <c r="S30" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3882,18 +3882,19 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3904,48 +3905,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134040822</v>
+        <v>134036147</v>
       </c>
       <c r="B31" t="n">
-        <v>99202</v>
+        <v>80474</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>594708</v>
+        <v>594500</v>
       </c>
       <c r="R31" t="n">
-        <v>7106124</v>
+        <v>7106009</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3974,7 +3975,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3984,7 +3985,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3993,19 +3994,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4905,10 +4905,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134036173</v>
+        <v>134041932</v>
       </c>
       <c r="B40" t="n">
-        <v>99202</v>
+        <v>80479</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4916,37 +4916,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>594691</v>
+        <v>594484</v>
       </c>
       <c r="R40" t="n">
-        <v>7106160</v>
+        <v>7106025</v>
       </c>
       <c r="S40" t="n">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5000,12 +5000,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5016,32 +5016,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134040828</v>
+        <v>134040824</v>
       </c>
       <c r="B41" t="n">
-        <v>92391</v>
+        <v>80368</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5051,10 +5051,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>594548</v>
+        <v>594761</v>
       </c>
       <c r="R41" t="n">
-        <v>7106114</v>
+        <v>7106145</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5127,32 +5127,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134040824</v>
+        <v>134040828</v>
       </c>
       <c r="B42" t="n">
-        <v>80368</v>
+        <v>92391</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5162,10 +5162,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>594761</v>
+        <v>594548</v>
       </c>
       <c r="R42" t="n">
-        <v>7106145</v>
+        <v>7106114</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5238,10 +5238,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134041932</v>
+        <v>134036173</v>
       </c>
       <c r="B43" t="n">
-        <v>80479</v>
+        <v>99202</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5249,37 +5249,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>594484</v>
+        <v>594691</v>
       </c>
       <c r="R43" t="n">
-        <v>7106025</v>
+        <v>7106160</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5333,12 +5333,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5349,48 +5349,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134036146</v>
+        <v>134041933</v>
       </c>
       <c r="B44" t="n">
-        <v>92391</v>
+        <v>80486</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>594500</v>
+        <v>594496</v>
       </c>
       <c r="R44" t="n">
-        <v>7106009</v>
+        <v>7106047</v>
       </c>
       <c r="S44" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5444,12 +5444,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5579,32 +5579,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134036177</v>
+        <v>134036146</v>
       </c>
       <c r="B46" t="n">
-        <v>92184</v>
+        <v>92391</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5614,13 +5614,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>594739</v>
+        <v>594500</v>
       </c>
       <c r="R46" t="n">
-        <v>7106142</v>
+        <v>7106009</v>
       </c>
       <c r="S46" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134041933</v>
+        <v>134036177</v>
       </c>
       <c r="B47" t="n">
-        <v>80486</v>
+        <v>92184</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5701,37 +5701,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>594496</v>
+        <v>594739</v>
       </c>
       <c r="R47" t="n">
-        <v>7106047</v>
+        <v>7106142</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5785,12 +5785,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5801,7 +5801,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134036171</v>
+        <v>134040809</v>
       </c>
       <c r="B48" t="n">
         <v>91973</v>
@@ -5832,17 +5832,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>594612</v>
+        <v>594482</v>
       </c>
       <c r="R48" t="n">
-        <v>7106094</v>
+        <v>7106066</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5896,12 +5896,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -6023,7 +6023,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134040809</v>
+        <v>134036171</v>
       </c>
       <c r="B50" t="n">
         <v>91973</v>
@@ -6054,17 +6054,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>594482</v>
+        <v>594612</v>
       </c>
       <c r="R50" t="n">
-        <v>7106066</v>
+        <v>7106094</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6118,12 +6118,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6134,48 +6134,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134036158</v>
+        <v>134041938</v>
       </c>
       <c r="B51" t="n">
-        <v>98051</v>
+        <v>91955</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221941</v>
+        <v>1108</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>594476</v>
+        <v>594721</v>
       </c>
       <c r="R51" t="n">
-        <v>7106135</v>
+        <v>7106166</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6229,12 +6229,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6245,32 +6245,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134036152</v>
+        <v>134036158</v>
       </c>
       <c r="B52" t="n">
-        <v>80474</v>
+        <v>98051</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6280,13 +6280,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>594475</v>
+        <v>594476</v>
       </c>
       <c r="R52" t="n">
-        <v>7106098</v>
+        <v>7106135</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6467,10 +6467,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134041938</v>
+        <v>134036152</v>
       </c>
       <c r="B54" t="n">
-        <v>91955</v>
+        <v>80474</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6478,34 +6478,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>594721</v>
+        <v>594475</v>
       </c>
       <c r="R54" t="n">
-        <v>7106166</v>
+        <v>7106098</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6562,12 +6562,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6697,10 +6697,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134036175</v>
+        <v>134040818</v>
       </c>
       <c r="B56" t="n">
-        <v>91979</v>
+        <v>91955</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6708,33 +6708,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>594758</v>
+        <v>594598</v>
       </c>
       <c r="R56" t="n">
-        <v>7106168</v>
+        <v>7106142</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6763,7 +6767,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6773,7 +6777,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6788,12 +6792,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6804,34 +6808,30 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134036163</v>
+        <v>134036175</v>
       </c>
       <c r="B57" t="n">
-        <v>80479</v>
+        <v>91979</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6839,13 +6839,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>594604</v>
+        <v>594758</v>
       </c>
       <c r="R57" t="n">
-        <v>7106104</v>
+        <v>7106168</v>
       </c>
       <c r="S57" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6915,48 +6915,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134040818</v>
+        <v>134036163</v>
       </c>
       <c r="B58" t="n">
-        <v>91955</v>
+        <v>80479</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>594598</v>
+        <v>594604</v>
       </c>
       <c r="R58" t="n">
-        <v>7106142</v>
+        <v>7106104</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7010,12 +7010,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7026,10 +7026,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134036145</v>
+        <v>134041937</v>
       </c>
       <c r="B59" t="n">
-        <v>91959</v>
+        <v>91955</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7037,37 +7037,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>594513</v>
+        <v>594714</v>
       </c>
       <c r="R59" t="n">
-        <v>7106004</v>
+        <v>7106130</v>
       </c>
       <c r="S59" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7121,12 +7121,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7137,10 +7137,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134041937</v>
+        <v>134036145</v>
       </c>
       <c r="B60" t="n">
-        <v>91955</v>
+        <v>91959</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7148,37 +7148,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>594714</v>
+        <v>594513</v>
       </c>
       <c r="R60" t="n">
-        <v>7106130</v>
+        <v>7106004</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7232,12 +7232,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">

--- a/artfynd/A 2278-2026 artfynd.xlsx
+++ b/artfynd/A 2278-2026 artfynd.xlsx
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134036167</v>
+        <v>134040810</v>
       </c>
       <c r="B10" t="n">
-        <v>96399</v>
+        <v>80486</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,37 +1586,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594607</v>
+        <v>594501</v>
       </c>
       <c r="R10" t="n">
-        <v>7106088</v>
+        <v>7106169</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,12 +1670,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1686,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134040810</v>
+        <v>134036167</v>
       </c>
       <c r="B11" t="n">
-        <v>80486</v>
+        <v>96399</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,37 +1697,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594501</v>
+        <v>594607</v>
       </c>
       <c r="R11" t="n">
-        <v>7106169</v>
+        <v>7106088</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,12 +1781,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2241,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134036149</v>
+        <v>134041934</v>
       </c>
       <c r="B16" t="n">
-        <v>57972</v>
+        <v>91980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,37 +2252,33 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594477</v>
+        <v>594559</v>
       </c>
       <c r="R16" t="n">
-        <v>7106037</v>
+        <v>7106144</v>
       </c>
       <c r="S16" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2311,7 +2307,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2321,7 +2317,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,12 +2332,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2352,10 +2348,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134041934</v>
+        <v>134036149</v>
       </c>
       <c r="B17" t="n">
-        <v>91980</v>
+        <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2363,33 +2359,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594559</v>
+        <v>594477</v>
       </c>
       <c r="R17" t="n">
-        <v>7106144</v>
+        <v>7106037</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2443,12 +2443,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2459,32 +2459,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134040806</v>
+        <v>134040808</v>
       </c>
       <c r="B18" t="n">
-        <v>91956</v>
+        <v>80486</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594500</v>
+        <v>594483</v>
       </c>
       <c r="R18" t="n">
-        <v>7106023</v>
+        <v>7106035</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2681,10 +2681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134036159</v>
+        <v>134040806</v>
       </c>
       <c r="B20" t="n">
-        <v>91980</v>
+        <v>91956</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2692,30 +2692,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594504</v>
+        <v>594500</v>
       </c>
       <c r="R20" t="n">
-        <v>7106148</v>
+        <v>7106023</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2747,7 +2751,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2757,7 +2761,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2772,12 +2776,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2788,34 +2792,30 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134036172</v>
+        <v>134036159</v>
       </c>
       <c r="B21" t="n">
-        <v>80368</v>
+        <v>91980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2823,13 +2823,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594619</v>
+        <v>594504</v>
       </c>
       <c r="R21" t="n">
-        <v>7106110</v>
+        <v>7106148</v>
       </c>
       <c r="S21" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2877,7 +2877,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2900,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134040808</v>
+        <v>134036172</v>
       </c>
       <c r="B22" t="n">
-        <v>80486</v>
+        <v>80368</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,37 +2910,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594483</v>
+        <v>594619</v>
       </c>
       <c r="R22" t="n">
-        <v>7106035</v>
+        <v>7106110</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2970,7 +2969,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2980,7 +2979,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,18 +2988,19 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3011,45 +3011,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134040814</v>
+        <v>134036155</v>
       </c>
       <c r="B23" t="n">
-        <v>91956</v>
+        <v>80424</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594524</v>
+        <v>594466</v>
       </c>
       <c r="R23" t="n">
-        <v>7106181</v>
+        <v>7106117</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3106,12 +3106,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3344,45 +3344,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134036155</v>
+        <v>134040814</v>
       </c>
       <c r="B26" t="n">
-        <v>80424</v>
+        <v>91956</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594466</v>
+        <v>594524</v>
       </c>
       <c r="R26" t="n">
-        <v>7106117</v>
+        <v>7106181</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3439,12 +3439,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3455,7 +3455,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134040815</v>
+        <v>134040807</v>
       </c>
       <c r="B27" t="n">
         <v>79359</v>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594571</v>
+        <v>594496</v>
       </c>
       <c r="R27" t="n">
-        <v>7106182</v>
+        <v>7106021</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3566,7 +3566,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134040807</v>
+        <v>134040815</v>
       </c>
       <c r="B28" t="n">
         <v>79359</v>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594496</v>
+        <v>594571</v>
       </c>
       <c r="R28" t="n">
-        <v>7106021</v>
+        <v>7106182</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4239,32 +4239,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134036151</v>
+        <v>134036157</v>
       </c>
       <c r="B34" t="n">
-        <v>91960</v>
+        <v>80368</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4274,13 +4274,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>594482</v>
+        <v>594474</v>
       </c>
       <c r="R34" t="n">
-        <v>7106077</v>
+        <v>7106125</v>
       </c>
       <c r="S34" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4350,10 +4350,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134036157</v>
+        <v>134040821</v>
       </c>
       <c r="B35" t="n">
-        <v>80368</v>
+        <v>99203</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4361,34 +4361,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>594474</v>
+        <v>594701</v>
       </c>
       <c r="R35" t="n">
-        <v>7106125</v>
+        <v>7106149</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4445,12 +4445,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4461,32 +4461,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134040821</v>
+        <v>134040827</v>
       </c>
       <c r="B36" t="n">
-        <v>99203</v>
+        <v>92231</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>594701</v>
+        <v>594535</v>
       </c>
       <c r="R36" t="n">
-        <v>7106149</v>
+        <v>7106124</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4572,10 +4572,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134040827</v>
+        <v>134036151</v>
       </c>
       <c r="B37" t="n">
-        <v>92231</v>
+        <v>91960</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4583,37 +4583,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>594535</v>
+        <v>594482</v>
       </c>
       <c r="R37" t="n">
-        <v>7106124</v>
+        <v>7106077</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,12 +4667,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4905,10 +4905,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134036173</v>
+        <v>134041932</v>
       </c>
       <c r="B40" t="n">
-        <v>99203</v>
+        <v>80479</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4916,37 +4916,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>594691</v>
+        <v>594484</v>
       </c>
       <c r="R40" t="n">
-        <v>7106160</v>
+        <v>7106025</v>
       </c>
       <c r="S40" t="n">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5000,12 +5000,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5016,10 +5016,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134041932</v>
+        <v>134040824</v>
       </c>
       <c r="B41" t="n">
-        <v>80479</v>
+        <v>80368</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5027,34 +5027,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>594484</v>
+        <v>594761</v>
       </c>
       <c r="R41" t="n">
-        <v>7106025</v>
+        <v>7106145</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5111,12 +5111,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5127,10 +5127,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134040824</v>
+        <v>134036173</v>
       </c>
       <c r="B42" t="n">
-        <v>80368</v>
+        <v>99203</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5138,37 +5138,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>594761</v>
+        <v>594691</v>
       </c>
       <c r="R42" t="n">
-        <v>7106145</v>
+        <v>7106160</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5222,12 +5222,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5349,53 +5349,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134036150</v>
+        <v>134041933</v>
       </c>
       <c r="B44" t="n">
-        <v>57975</v>
+        <v>80486</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>594479</v>
+        <v>594496</v>
       </c>
       <c r="R44" t="n">
-        <v>7106056</v>
+        <v>7106047</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5427,7 +5419,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5437,14 +5429,14 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="b">
         <v>0</v>
@@ -5452,12 +5444,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5468,48 +5460,56 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134036146</v>
+        <v>134036150</v>
       </c>
       <c r="B45" t="n">
-        <v>92392</v>
+        <v>57975</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>594500</v>
+        <v>594479</v>
       </c>
       <c r="R45" t="n">
-        <v>7106009</v>
+        <v>7106056</v>
       </c>
       <c r="S45" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5548,14 +5548,14 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG45" t="b">
         <v>0</v>
@@ -5690,48 +5690,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134041933</v>
+        <v>134036146</v>
       </c>
       <c r="B47" t="n">
-        <v>80486</v>
+        <v>92392</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>594496</v>
+        <v>594500</v>
       </c>
       <c r="R47" t="n">
-        <v>7106047</v>
+        <v>7106009</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5785,12 +5785,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5801,7 +5801,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134040809</v>
+        <v>134036171</v>
       </c>
       <c r="B48" t="n">
         <v>91974</v>
@@ -5832,17 +5832,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>594482</v>
+        <v>594612</v>
       </c>
       <c r="R48" t="n">
-        <v>7106066</v>
+        <v>7106094</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5896,12 +5896,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -6023,7 +6023,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134036171</v>
+        <v>134040809</v>
       </c>
       <c r="B50" t="n">
         <v>91974</v>
@@ -6054,17 +6054,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>594612</v>
+        <v>594482</v>
       </c>
       <c r="R50" t="n">
-        <v>7106094</v>
+        <v>7106066</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6118,12 +6118,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6134,48 +6134,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134036158</v>
+        <v>134041938</v>
       </c>
       <c r="B51" t="n">
-        <v>98052</v>
+        <v>91956</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221941</v>
+        <v>1108</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>594476</v>
+        <v>594721</v>
       </c>
       <c r="R51" t="n">
-        <v>7106135</v>
+        <v>7106166</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6229,12 +6229,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6467,48 +6467,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134041938</v>
+        <v>134036158</v>
       </c>
       <c r="B54" t="n">
-        <v>91956</v>
+        <v>98052</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>221941</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>594721</v>
+        <v>594476</v>
       </c>
       <c r="R54" t="n">
-        <v>7106166</v>
+        <v>7106135</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6562,12 +6562,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6697,10 +6697,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134036175</v>
+        <v>134040818</v>
       </c>
       <c r="B56" t="n">
-        <v>91980</v>
+        <v>91956</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6708,33 +6708,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>594758</v>
+        <v>594598</v>
       </c>
       <c r="R56" t="n">
-        <v>7106168</v>
+        <v>7106142</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6763,7 +6767,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6773,7 +6777,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6788,12 +6792,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6804,34 +6808,30 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134036163</v>
+        <v>134036175</v>
       </c>
       <c r="B57" t="n">
-        <v>80479</v>
+        <v>91980</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6839,13 +6839,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>594604</v>
+        <v>594758</v>
       </c>
       <c r="R57" t="n">
-        <v>7106104</v>
+        <v>7106168</v>
       </c>
       <c r="S57" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6915,48 +6915,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134040818</v>
+        <v>134036163</v>
       </c>
       <c r="B58" t="n">
-        <v>91956</v>
+        <v>80479</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>594598</v>
+        <v>594604</v>
       </c>
       <c r="R58" t="n">
-        <v>7106142</v>
+        <v>7106104</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7010,12 +7010,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">

--- a/artfynd/A 2278-2026 artfynd.xlsx
+++ b/artfynd/A 2278-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>134004112</v>
       </c>
       <c r="B3" t="n">
-        <v>80479</v>
+        <v>80486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>134004114</v>
       </c>
       <c r="B5" t="n">
-        <v>92231</v>
+        <v>92238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134005846</v>
+        <v>134004111</v>
       </c>
       <c r="B8" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,17 +1388,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>a 2278-2026, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594599</v>
+        <v>594815</v>
       </c>
       <c r="R8" t="n">
-        <v>7106170</v>
+        <v>7106147</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,22 +1452,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134004111</v>
+        <v>134005846</v>
       </c>
       <c r="B9" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,17 +1499,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>a 2278-2026, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594815</v>
+        <v>594599</v>
       </c>
       <c r="R9" t="n">
-        <v>7106147</v>
+        <v>7106170</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,26 +1563,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Patrik Eriksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134040810</v>
+        <v>134036167</v>
       </c>
       <c r="B10" t="n">
-        <v>80486</v>
+        <v>96406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,37 +1586,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594501</v>
+        <v>594607</v>
       </c>
       <c r="R10" t="n">
-        <v>7106169</v>
+        <v>7106088</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,12 +1670,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1686,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134036167</v>
+        <v>134040810</v>
       </c>
       <c r="B11" t="n">
-        <v>96399</v>
+        <v>80493</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,37 +1697,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594607</v>
+        <v>594501</v>
       </c>
       <c r="R11" t="n">
-        <v>7106088</v>
+        <v>7106169</v>
       </c>
       <c r="S11" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,12 +1781,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1800,7 +1800,7 @@
         <v>134040804</v>
       </c>
       <c r="B12" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>134040826</v>
       </c>
       <c r="B13" t="n">
-        <v>96399</v>
+        <v>96406</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134040803</v>
+        <v>134040813</v>
       </c>
       <c r="B14" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,13 +2054,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594534</v>
+        <v>594504</v>
       </c>
       <c r="R14" t="n">
-        <v>7105996</v>
+        <v>7106177</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134040813</v>
+        <v>134040803</v>
       </c>
       <c r="B15" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594504</v>
+        <v>594534</v>
       </c>
       <c r="R15" t="n">
-        <v>7106177</v>
+        <v>7105996</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2244,7 +2244,7 @@
         <v>134041934</v>
       </c>
       <c r="B16" t="n">
-        <v>91980</v>
+        <v>91987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2459,10 +2459,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134040808</v>
+        <v>134036160</v>
       </c>
       <c r="B18" t="n">
-        <v>80486</v>
+        <v>96406</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2470,37 +2470,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>2809</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594483</v>
+        <v>594497</v>
       </c>
       <c r="R18" t="n">
-        <v>7106035</v>
+        <v>7106164</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2554,12 +2554,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2570,34 +2570,30 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134036160</v>
+        <v>134036159</v>
       </c>
       <c r="B19" t="n">
-        <v>96399</v>
+        <v>91987</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2605,13 +2601,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594497</v>
+        <v>594504</v>
       </c>
       <c r="R19" t="n">
-        <v>7106164</v>
+        <v>7106148</v>
       </c>
       <c r="S19" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2640,7 +2636,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2650,7 +2646,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2681,48 +2677,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134040806</v>
+        <v>134036172</v>
       </c>
       <c r="B20" t="n">
-        <v>91956</v>
+        <v>80375</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594500</v>
+        <v>594619</v>
       </c>
       <c r="R20" t="n">
-        <v>7106023</v>
+        <v>7106110</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2751,7 +2747,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2761,7 +2757,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,18 +2766,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2792,10 +2789,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134036159</v>
+        <v>134040806</v>
       </c>
       <c r="B21" t="n">
-        <v>91980</v>
+        <v>91963</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,30 +2800,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594504</v>
+        <v>594500</v>
       </c>
       <c r="R21" t="n">
-        <v>7106148</v>
+        <v>7106023</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2858,7 +2859,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2868,7 +2869,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2883,12 +2884,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2899,10 +2900,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134036172</v>
+        <v>134040808</v>
       </c>
       <c r="B22" t="n">
-        <v>80368</v>
+        <v>80493</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,37 +2911,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594619</v>
+        <v>594483</v>
       </c>
       <c r="R22" t="n">
-        <v>7106110</v>
+        <v>7106035</v>
       </c>
       <c r="S22" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2969,7 +2970,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2979,7 +2980,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2988,19 +2989,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3011,45 +3011,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134036155</v>
+        <v>134040814</v>
       </c>
       <c r="B23" t="n">
-        <v>80424</v>
+        <v>91963</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594466</v>
+        <v>594524</v>
       </c>
       <c r="R23" t="n">
-        <v>7106117</v>
+        <v>7106181</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3106,12 +3106,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3125,7 +3125,7 @@
         <v>134036154</v>
       </c>
       <c r="B24" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>134036169</v>
       </c>
       <c r="B25" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,45 +3344,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134040814</v>
+        <v>134036155</v>
       </c>
       <c r="B26" t="n">
-        <v>91956</v>
+        <v>80431</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594524</v>
+        <v>594466</v>
       </c>
       <c r="R26" t="n">
-        <v>7106181</v>
+        <v>7106117</v>
       </c>
       <c r="S26" t="n">
         <v>8</v>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3439,12 +3439,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3455,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134040807</v>
+        <v>134040815</v>
       </c>
       <c r="B27" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594496</v>
+        <v>594571</v>
       </c>
       <c r="R27" t="n">
-        <v>7106021</v>
+        <v>7106182</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134040815</v>
+        <v>134040807</v>
       </c>
       <c r="B28" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594571</v>
+        <v>594496</v>
       </c>
       <c r="R28" t="n">
-        <v>7106182</v>
+        <v>7106021</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3680,7 +3680,7 @@
         <v>134036168</v>
       </c>
       <c r="B29" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3793,48 +3793,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134040822</v>
+        <v>134036147</v>
       </c>
       <c r="B30" t="n">
-        <v>99203</v>
+        <v>80481</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>594708</v>
+        <v>594500</v>
       </c>
       <c r="R30" t="n">
-        <v>7106124</v>
+        <v>7106009</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3882,19 +3882,18 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3905,48 +3904,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134036147</v>
+        <v>134040822</v>
       </c>
       <c r="B31" t="n">
-        <v>80474</v>
+        <v>99210</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>594500</v>
+        <v>594708</v>
       </c>
       <c r="R31" t="n">
-        <v>7106009</v>
+        <v>7106124</v>
       </c>
       <c r="S31" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3975,7 +3974,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3985,7 +3984,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3994,18 +3993,19 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4019,7 +4019,7 @@
         <v>134036161</v>
       </c>
       <c r="B32" t="n">
-        <v>80368</v>
+        <v>80375</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>134040805</v>
       </c>
       <c r="B33" t="n">
-        <v>80486</v>
+        <v>80493</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4239,32 +4239,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134036157</v>
+        <v>134036151</v>
       </c>
       <c r="B34" t="n">
-        <v>80368</v>
+        <v>91967</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4274,13 +4274,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>594474</v>
+        <v>594482</v>
       </c>
       <c r="R34" t="n">
-        <v>7106125</v>
+        <v>7106077</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4350,10 +4350,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134040821</v>
+        <v>134036157</v>
       </c>
       <c r="B35" t="n">
-        <v>99203</v>
+        <v>80375</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4361,34 +4361,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>594701</v>
+        <v>594474</v>
       </c>
       <c r="R35" t="n">
-        <v>7106149</v>
+        <v>7106125</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4445,12 +4445,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4461,32 +4461,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134040827</v>
+        <v>134040821</v>
       </c>
       <c r="B36" t="n">
-        <v>92231</v>
+        <v>99210</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>594535</v>
+        <v>594701</v>
       </c>
       <c r="R36" t="n">
-        <v>7106124</v>
+        <v>7106149</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4572,10 +4572,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134036151</v>
+        <v>134040827</v>
       </c>
       <c r="B37" t="n">
-        <v>91960</v>
+        <v>92238</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4583,37 +4583,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>594482</v>
+        <v>594535</v>
       </c>
       <c r="R37" t="n">
-        <v>7106077</v>
+        <v>7106124</v>
       </c>
       <c r="S37" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,12 +4667,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4683,48 +4683,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134036165</v>
+        <v>134040825</v>
       </c>
       <c r="B38" t="n">
-        <v>80486</v>
+        <v>79366</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>594602</v>
+        <v>594826</v>
       </c>
       <c r="R38" t="n">
-        <v>7106101</v>
+        <v>7106126</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4778,12 +4778,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4794,48 +4794,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134040825</v>
+        <v>134036165</v>
       </c>
       <c r="B39" t="n">
-        <v>79359</v>
+        <v>80493</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>594826</v>
+        <v>594602</v>
       </c>
       <c r="R39" t="n">
-        <v>7106126</v>
+        <v>7106101</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4889,12 +4889,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4905,10 +4905,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134041932</v>
+        <v>134040824</v>
       </c>
       <c r="B40" t="n">
-        <v>80479</v>
+        <v>80375</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4916,34 +4916,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>594484</v>
+        <v>594761</v>
       </c>
       <c r="R40" t="n">
-        <v>7106025</v>
+        <v>7106145</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5000,12 +5000,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5016,32 +5016,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134040824</v>
+        <v>134040828</v>
       </c>
       <c r="B41" t="n">
-        <v>80368</v>
+        <v>92399</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5051,10 +5051,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>594761</v>
+        <v>594548</v>
       </c>
       <c r="R41" t="n">
-        <v>7106145</v>
+        <v>7106114</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5127,10 +5127,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134036173</v>
+        <v>134041932</v>
       </c>
       <c r="B42" t="n">
-        <v>99203</v>
+        <v>80486</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5138,37 +5138,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>594691</v>
+        <v>594484</v>
       </c>
       <c r="R42" t="n">
-        <v>7106160</v>
+        <v>7106025</v>
       </c>
       <c r="S42" t="n">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5222,12 +5222,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5238,48 +5238,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134040828</v>
+        <v>134036173</v>
       </c>
       <c r="B43" t="n">
-        <v>92392</v>
+        <v>99210</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>594548</v>
+        <v>594691</v>
       </c>
       <c r="R43" t="n">
-        <v>7106114</v>
+        <v>7106160</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5333,12 +5333,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5349,45 +5349,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134041933</v>
+        <v>134036150</v>
       </c>
       <c r="B44" t="n">
-        <v>80486</v>
+        <v>57975</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>594496</v>
+        <v>594479</v>
       </c>
       <c r="R44" t="n">
-        <v>7106047</v>
+        <v>7106056</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5419,7 +5427,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5429,14 +5437,14 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG44" t="b">
         <v>0</v>
@@ -5444,12 +5452,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5460,56 +5468,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134036150</v>
+        <v>134036177</v>
       </c>
       <c r="B45" t="n">
-        <v>57975</v>
+        <v>92192</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>594479</v>
+        <v>594739</v>
       </c>
       <c r="R45" t="n">
-        <v>7106056</v>
+        <v>7106142</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5548,14 +5548,14 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="b">
         <v>0</v>
@@ -5579,32 +5579,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134036177</v>
+        <v>134036146</v>
       </c>
       <c r="B46" t="n">
-        <v>92185</v>
+        <v>92399</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5614,13 +5614,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>594739</v>
+        <v>594500</v>
       </c>
       <c r="R46" t="n">
-        <v>7106142</v>
+        <v>7106009</v>
       </c>
       <c r="S46" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5690,48 +5690,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134036146</v>
+        <v>134041933</v>
       </c>
       <c r="B47" t="n">
-        <v>92392</v>
+        <v>80493</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>594500</v>
+        <v>594496</v>
       </c>
       <c r="R47" t="n">
-        <v>7106009</v>
+        <v>7106047</v>
       </c>
       <c r="S47" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5785,12 +5785,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5804,7 +5804,7 @@
         <v>134036171</v>
       </c>
       <c r="B48" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>134036170</v>
       </c>
       <c r="B49" t="n">
-        <v>92675</v>
+        <v>92682</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>134040809</v>
       </c>
       <c r="B50" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>134041938</v>
       </c>
       <c r="B51" t="n">
-        <v>91956</v>
+        <v>91963</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6245,32 +6245,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134036179</v>
+        <v>134036158</v>
       </c>
       <c r="B52" t="n">
-        <v>91960</v>
+        <v>98059</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6280,13 +6280,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>594582</v>
+        <v>594476</v>
       </c>
       <c r="R52" t="n">
-        <v>7106116</v>
+        <v>7106135</v>
       </c>
       <c r="S52" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6359,7 +6359,7 @@
         <v>134036152</v>
       </c>
       <c r="B53" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6467,32 +6467,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134036158</v>
+        <v>134036179</v>
       </c>
       <c r="B54" t="n">
-        <v>98052</v>
+        <v>91967</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6502,13 +6502,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>594476</v>
+        <v>594582</v>
       </c>
       <c r="R54" t="n">
-        <v>7106135</v>
+        <v>7106116</v>
       </c>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6581,7 +6581,7 @@
         <v>134040817</v>
       </c>
       <c r="B55" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6697,48 +6697,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134040818</v>
+        <v>134036163</v>
       </c>
       <c r="B56" t="n">
-        <v>91956</v>
+        <v>80486</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>594598</v>
+        <v>594604</v>
       </c>
       <c r="R56" t="n">
-        <v>7106142</v>
+        <v>7106104</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6792,12 +6792,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6811,7 +6811,7 @@
         <v>134036175</v>
       </c>
       <c r="B57" t="n">
-        <v>91980</v>
+        <v>91987</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6915,48 +6915,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134036163</v>
+        <v>134040818</v>
       </c>
       <c r="B58" t="n">
-        <v>80479</v>
+        <v>91963</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>594604</v>
+        <v>594598</v>
       </c>
       <c r="R58" t="n">
-        <v>7106104</v>
+        <v>7106142</v>
       </c>
       <c r="S58" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7010,12 +7010,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7026,10 +7026,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134036145</v>
+        <v>134041937</v>
       </c>
       <c r="B59" t="n">
-        <v>91960</v>
+        <v>91963</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7037,37 +7037,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>594513</v>
+        <v>594714</v>
       </c>
       <c r="R59" t="n">
-        <v>7106004</v>
+        <v>7106130</v>
       </c>
       <c r="S59" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7121,12 +7121,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7137,10 +7137,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134041937</v>
+        <v>134036145</v>
       </c>
       <c r="B60" t="n">
-        <v>91956</v>
+        <v>91967</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7148,37 +7148,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>594714</v>
+        <v>594513</v>
       </c>
       <c r="R60" t="n">
-        <v>7106130</v>
+        <v>7106004</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7232,12 +7232,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7251,7 +7251,7 @@
         <v>134086724</v>
       </c>
       <c r="B61" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>134040812</v>
       </c>
       <c r="B62" t="n">
-        <v>83349</v>
+        <v>83356</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 2278-2026 artfynd.xlsx
+++ b/artfynd/A 2278-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1606395</v>
+        <v>134040802</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>S Lomsjö, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594681.4413321712</v>
+        <v>594530</v>
       </c>
       <c r="R2" t="n">
-        <v>7106191.952509125</v>
+        <v>7105970</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-09-06</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-09-06</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,44 +770,48 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134004112</v>
+        <v>134004114</v>
       </c>
       <c r="B3" t="n">
-        <v>80486</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594779</v>
+        <v>594697</v>
       </c>
       <c r="R3" t="n">
-        <v>7106096</v>
+        <v>7106106</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134004110</v>
+        <v>134040801</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>92245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,37 +908,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>a 2278-2026, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594497</v>
+        <v>594530</v>
       </c>
       <c r="R4" t="n">
-        <v>7106185</v>
+        <v>7105969</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,12 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,12 +992,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1014,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134004114</v>
+        <v>134040827</v>
       </c>
       <c r="B5" t="n">
-        <v>92238</v>
+        <v>92245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,14 +1039,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>a 2278-2026, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594697</v>
+        <v>594535</v>
       </c>
       <c r="R5" t="n">
-        <v>7106106</v>
+        <v>7106124</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,12 +1103,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1125,45 +1119,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134004120</v>
+        <v>134036170</v>
       </c>
       <c r="B6" t="n">
-        <v>58839</v>
+        <v>92689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208249</v>
+        <v>898</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>a 2278-2026, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594671</v>
+        <v>594612</v>
       </c>
       <c r="R6" t="n">
-        <v>7106200</v>
+        <v>7106097</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1195,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,19 +1208,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1237,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134004119</v>
+        <v>134040806</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>91970</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1248,38 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>a 2278-2026, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594745</v>
+        <v>594500</v>
       </c>
       <c r="R7" t="n">
-        <v>7106148</v>
+        <v>7106023</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1321,19 +1310,14 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>osäker fynd</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1341,12 +1325,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1357,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134004111</v>
+        <v>134040814</v>
       </c>
       <c r="B8" t="n">
-        <v>79366</v>
+        <v>91970</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,37 +1352,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>a 2278-2026, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594815</v>
+        <v>594524</v>
       </c>
       <c r="R8" t="n">
-        <v>7106147</v>
+        <v>7106181</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,12 +1436,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1468,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134005846</v>
+        <v>134040818</v>
       </c>
       <c r="B9" t="n">
-        <v>79366</v>
+        <v>91970</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,34 +1463,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594599</v>
+        <v>594598</v>
       </c>
       <c r="R9" t="n">
-        <v>7106170</v>
+        <v>7106142</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1538,7 +1522,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1532,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,60 +1547,64 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134036167</v>
+        <v>134041937</v>
       </c>
       <c r="B10" t="n">
-        <v>96406</v>
+        <v>91970</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594607</v>
+        <v>594714</v>
       </c>
       <c r="R10" t="n">
-        <v>7106088</v>
+        <v>7106130</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,7 +1633,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1655,7 +1643,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,12 +1658,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1686,45 +1674,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134040810</v>
+        <v>134041938</v>
       </c>
       <c r="B11" t="n">
-        <v>80493</v>
+        <v>91970</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594501</v>
+        <v>594721</v>
       </c>
       <c r="R11" t="n">
-        <v>7106169</v>
+        <v>7106166</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,7 +1744,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1754,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,12 +1769,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1797,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134040804</v>
+        <v>134036145</v>
       </c>
       <c r="B12" t="n">
-        <v>79366</v>
+        <v>91974</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,37 +1796,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594523</v>
+        <v>594513</v>
       </c>
       <c r="R12" t="n">
-        <v>7106019</v>
+        <v>7106004</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1867,7 +1855,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1877,7 +1865,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,12 +1880,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1908,48 +1896,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134040826</v>
+        <v>134036151</v>
       </c>
       <c r="B13" t="n">
-        <v>96406</v>
+        <v>91974</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594724</v>
+        <v>594482</v>
       </c>
       <c r="R13" t="n">
-        <v>7106118</v>
+        <v>7106077</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1978,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1988,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,12 +1991,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2019,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134040813</v>
+        <v>134036169</v>
       </c>
       <c r="B14" t="n">
-        <v>79366</v>
+        <v>91974</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,37 +2018,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594504</v>
+        <v>594612</v>
       </c>
       <c r="R14" t="n">
-        <v>7106177</v>
+        <v>7106097</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2087,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,12 +2102,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2130,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134040803</v>
+        <v>134036179</v>
       </c>
       <c r="B15" t="n">
-        <v>79366</v>
+        <v>91974</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,37 +2129,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594534</v>
+        <v>594582</v>
       </c>
       <c r="R15" t="n">
-        <v>7105996</v>
+        <v>7106116</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2188,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2198,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,12 +2213,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2241,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134041934</v>
+        <v>134040800</v>
       </c>
       <c r="B16" t="n">
-        <v>91987</v>
+        <v>91974</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,33 +2240,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594559</v>
+        <v>594524</v>
       </c>
       <c r="R16" t="n">
-        <v>7106144</v>
+        <v>7105970</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2307,7 +2299,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2317,7 +2309,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2332,12 +2324,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2348,48 +2340,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134036149</v>
+        <v>373213</v>
       </c>
       <c r="B17" t="n">
-        <v>57972</v>
+        <v>91923</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>S Lomsjö, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594477</v>
+        <v>594534</v>
       </c>
       <c r="R17" t="n">
-        <v>7106037</v>
+        <v>7106059</v>
       </c>
       <c r="S17" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2413,22 +2405,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:06</t>
+          <t>2012-09-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:06</t>
+          <t>2012-09-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2443,48 +2425,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134036160</v>
+        <v>134036154</v>
       </c>
       <c r="B18" t="n">
-        <v>96406</v>
+        <v>91988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2809</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2494,13 +2472,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594497</v>
+        <v>594480</v>
       </c>
       <c r="R18" t="n">
-        <v>7106164</v>
+        <v>7106126</v>
       </c>
       <c r="S18" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2529,7 +2507,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2539,7 +2517,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2570,30 +2548,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134036159</v>
+        <v>134036171</v>
       </c>
       <c r="B19" t="n">
-        <v>91987</v>
+        <v>91988</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2601,13 +2583,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594504</v>
+        <v>594612</v>
       </c>
       <c r="R19" t="n">
-        <v>7106148</v>
+        <v>7106094</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2636,7 +2618,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2646,7 +2628,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2677,48 +2659,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134036172</v>
+        <v>134040809</v>
       </c>
       <c r="B20" t="n">
-        <v>80375</v>
+        <v>91988</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>594619</v>
+        <v>594482</v>
       </c>
       <c r="R20" t="n">
-        <v>7106110</v>
+        <v>7106066</v>
       </c>
       <c r="S20" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2747,7 +2729,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2757,7 +2739,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2766,19 +2748,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2789,10 +2770,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134040806</v>
+        <v>134036146</v>
       </c>
       <c r="B21" t="n">
-        <v>91963</v>
+        <v>92406</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2800,37 +2781,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
         <v>594500</v>
       </c>
       <c r="R21" t="n">
-        <v>7106023</v>
+        <v>7106009</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2859,7 +2840,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2869,7 +2850,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2884,12 +2865,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2900,32 +2881,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134040808</v>
+        <v>134040828</v>
       </c>
       <c r="B22" t="n">
-        <v>80493</v>
+        <v>92406</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2935,10 +2916,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>594483</v>
+        <v>594548</v>
       </c>
       <c r="R22" t="n">
-        <v>7106035</v>
+        <v>7106114</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2970,7 +2951,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2980,7 +2961,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3011,10 +2992,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134040814</v>
+        <v>134040812</v>
       </c>
       <c r="B23" t="n">
-        <v>91963</v>
+        <v>83363</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3022,21 +3003,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3046,13 +3027,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>594524</v>
+        <v>594508</v>
       </c>
       <c r="R23" t="n">
-        <v>7106181</v>
+        <v>7106172</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3081,7 +3062,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3091,7 +3072,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3122,10 +3103,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134036154</v>
+        <v>422253</v>
       </c>
       <c r="B24" t="n">
-        <v>91981</v>
+        <v>92097</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,37 +3114,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>1588</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>S Lomsjö, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>594480</v>
+        <v>594581</v>
       </c>
       <c r="R24" t="n">
-        <v>7106126</v>
+        <v>7106066</v>
       </c>
       <c r="S24" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3187,22 +3168,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:18</t>
+          <t>2012-09-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:18</t>
+          <t>2012-09-06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3217,48 +3188,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134036169</v>
+        <v>134036160</v>
       </c>
       <c r="B25" t="n">
-        <v>91967</v>
+        <v>96413</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3268,13 +3235,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>594612</v>
+        <v>594497</v>
       </c>
       <c r="R25" t="n">
-        <v>7106097</v>
+        <v>7106164</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3303,7 +3270,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3313,7 +3280,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3344,10 +3311,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134036155</v>
+        <v>134036167</v>
       </c>
       <c r="B26" t="n">
-        <v>80431</v>
+        <v>96413</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3355,21 +3322,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>2809</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3379,13 +3346,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>594466</v>
+        <v>594607</v>
       </c>
       <c r="R26" t="n">
-        <v>7106117</v>
+        <v>7106088</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3414,7 +3381,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3424,7 +3391,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3455,32 +3422,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134040815</v>
+        <v>134040826</v>
       </c>
       <c r="B27" t="n">
-        <v>79366</v>
+        <v>96413</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3490,13 +3457,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>594571</v>
+        <v>594724</v>
       </c>
       <c r="R27" t="n">
-        <v>7106182</v>
+        <v>7106118</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3525,7 +3492,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3535,7 +3502,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3566,48 +3533,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134040807</v>
+        <v>134036177</v>
       </c>
       <c r="B28" t="n">
-        <v>79366</v>
+        <v>92199</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>594496</v>
+        <v>594739</v>
       </c>
       <c r="R28" t="n">
-        <v>7106021</v>
+        <v>7106142</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3636,7 +3603,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3646,7 +3613,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3661,12 +3628,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3677,48 +3644,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134036168</v>
+        <v>134040829</v>
       </c>
       <c r="B29" t="n">
-        <v>79366</v>
+        <v>92199</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>594610</v>
+        <v>594506</v>
       </c>
       <c r="R29" t="n">
-        <v>7106086</v>
+        <v>7106075</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3747,7 +3714,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3757,12 +3724,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt. Med apotecier</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3777,12 +3739,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3793,48 +3755,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134036147</v>
+        <v>1353227</v>
       </c>
       <c r="B30" t="n">
-        <v>80481</v>
+        <v>92836</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>4740</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sotriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius lignyotus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>S Lomsjö, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>594500</v>
+        <v>594687</v>
       </c>
       <c r="R30" t="n">
-        <v>7106009</v>
+        <v>7106212</v>
       </c>
       <c r="S30" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3858,22 +3820,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2012-09-06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2012-09-06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3888,26 +3840,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134040822</v>
+        <v>1606395</v>
       </c>
       <c r="B31" t="n">
-        <v>99210</v>
+        <v>91872</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3915,34 +3863,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>S Lomsjö, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>594708</v>
+        <v>594681</v>
       </c>
       <c r="R31" t="n">
-        <v>7106124</v>
+        <v>7106192</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3969,22 +3917,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:48</t>
+          <t>2012-09-06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:48</t>
+          <t>2012-09-06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3993,71 +3931,66 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134036161</v>
+        <v>134004111</v>
       </c>
       <c r="B32" t="n">
-        <v>80375</v>
+        <v>79373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>a 2278-2026, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>594560</v>
+        <v>594815</v>
       </c>
       <c r="R32" t="n">
-        <v>7106080</v>
+        <v>7106147</v>
       </c>
       <c r="S32" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4086,7 +4019,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4096,7 +4029,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4105,19 +4038,18 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4128,45 +4060,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134040805</v>
+        <v>134004113</v>
       </c>
       <c r="B33" t="n">
-        <v>80493</v>
+        <v>79373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>a 2278-2026, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>594524</v>
+        <v>594728</v>
       </c>
       <c r="R33" t="n">
-        <v>7106017</v>
+        <v>7106103</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4198,7 +4130,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4208,7 +4140,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4223,12 +4155,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4239,48 +4171,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134036151</v>
+        <v>134004115</v>
       </c>
       <c r="B34" t="n">
-        <v>91967</v>
+        <v>79373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>a 2278-2026, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>594482</v>
+        <v>594671</v>
       </c>
       <c r="R34" t="n">
-        <v>7106077</v>
+        <v>7106094</v>
       </c>
       <c r="S34" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4309,7 +4241,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,7 +4251,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4334,12 +4266,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4350,45 +4282,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134036157</v>
+        <v>134004117</v>
       </c>
       <c r="B35" t="n">
-        <v>80375</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>a 2278-2026, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>594474</v>
+        <v>594582</v>
       </c>
       <c r="R35" t="n">
-        <v>7106125</v>
+        <v>7106061</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4420,7 +4352,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4430,7 +4362,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4445,12 +4377,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4461,45 +4393,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134040821</v>
+        <v>134005846</v>
       </c>
       <c r="B36" t="n">
-        <v>99210</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>594701</v>
+        <v>594599</v>
       </c>
       <c r="R36" t="n">
-        <v>7106149</v>
+        <v>7106170</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4531,7 +4463,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4541,7 +4473,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4556,64 +4488,60 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Patrik Eriksson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134040827</v>
+        <v>134036168</v>
       </c>
       <c r="B37" t="n">
-        <v>92238</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>594535</v>
+        <v>594610</v>
       </c>
       <c r="R37" t="n">
-        <v>7106124</v>
+        <v>7106086</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4642,7 +4570,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4652,7 +4580,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt. Med apotecier</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,12 +4600,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4683,14 +4616,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134040825</v>
+        <v>134040803</v>
       </c>
       <c r="B38" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4718,10 +4651,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>594826</v>
+        <v>594534</v>
       </c>
       <c r="R38" t="n">
-        <v>7106126</v>
+        <v>7105996</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4753,7 +4686,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4763,7 +4696,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4794,48 +4727,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134036165</v>
+        <v>134040804</v>
       </c>
       <c r="B39" t="n">
-        <v>80493</v>
+        <v>79373</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>594602</v>
+        <v>594523</v>
       </c>
       <c r="R39" t="n">
-        <v>7106101</v>
+        <v>7106019</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4864,7 +4797,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4874,7 +4807,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4889,12 +4822,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4905,32 +4838,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134040824</v>
+        <v>134040807</v>
       </c>
       <c r="B40" t="n">
-        <v>80375</v>
+        <v>79373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4940,10 +4873,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>594761</v>
+        <v>594496</v>
       </c>
       <c r="R40" t="n">
-        <v>7106145</v>
+        <v>7106021</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4975,7 +4908,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4985,7 +4918,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5016,10 +4949,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134040828</v>
+        <v>134040813</v>
       </c>
       <c r="B41" t="n">
-        <v>92399</v>
+        <v>79373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5027,21 +4960,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5051,13 +4984,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>594548</v>
+        <v>594504</v>
       </c>
       <c r="R41" t="n">
-        <v>7106114</v>
+        <v>7106177</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5086,7 +5019,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5096,7 +5029,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5127,45 +5060,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134041932</v>
+        <v>134040815</v>
       </c>
       <c r="B42" t="n">
-        <v>80486</v>
+        <v>79373</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>594484</v>
+        <v>594571</v>
       </c>
       <c r="R42" t="n">
-        <v>7106025</v>
+        <v>7106182</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5197,7 +5130,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5207,7 +5140,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5222,12 +5155,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5238,48 +5171,55 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134036173</v>
+        <v>134040817</v>
       </c>
       <c r="B43" t="n">
-        <v>99210</v>
+        <v>79373</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>594691</v>
+        <v>594576</v>
       </c>
       <c r="R43" t="n">
-        <v>7106160</v>
+        <v>7106159</v>
       </c>
       <c r="S43" t="n">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5308,7 +5248,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5318,7 +5258,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5327,18 +5267,19 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5349,53 +5290,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134036150</v>
+        <v>134040825</v>
       </c>
       <c r="B44" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>594479</v>
+        <v>594826</v>
       </c>
       <c r="R44" t="n">
-        <v>7106056</v>
+        <v>7106126</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5427,7 +5360,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5437,14 +5370,14 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="b">
         <v>0</v>
@@ -5452,12 +5385,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5468,10 +5401,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134036177</v>
+        <v>134036157</v>
       </c>
       <c r="B45" t="n">
-        <v>92192</v>
+        <v>80382</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5479,21 +5412,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3298</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5503,13 +5436,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>594739</v>
+        <v>594474</v>
       </c>
       <c r="R45" t="n">
-        <v>7106142</v>
+        <v>7106125</v>
       </c>
       <c r="S45" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5538,7 +5471,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5548,7 +5481,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5579,32 +5512,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134036146</v>
+        <v>134036161</v>
       </c>
       <c r="B46" t="n">
-        <v>92399</v>
+        <v>80382</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5614,13 +5547,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>594500</v>
+        <v>594560</v>
       </c>
       <c r="R46" t="n">
-        <v>7106009</v>
+        <v>7106080</v>
       </c>
       <c r="S46" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5649,7 +5582,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5659,7 +5592,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5668,6 +5601,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5690,10 +5624,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134041933</v>
+        <v>134036172</v>
       </c>
       <c r="B47" t="n">
-        <v>80493</v>
+        <v>80382</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5701,37 +5635,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>594496</v>
+        <v>594619</v>
       </c>
       <c r="R47" t="n">
-        <v>7106047</v>
+        <v>7106110</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5760,7 +5694,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5770,7 +5704,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5779,18 +5713,19 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5801,48 +5736,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134036171</v>
+        <v>134040824</v>
       </c>
       <c r="B48" t="n">
-        <v>91981</v>
+        <v>80382</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1204</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>594612</v>
+        <v>594761</v>
       </c>
       <c r="R48" t="n">
-        <v>7106094</v>
+        <v>7106145</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5871,7 +5806,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5881,7 +5816,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5896,12 +5831,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5912,32 +5847,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134036170</v>
+        <v>134005847</v>
       </c>
       <c r="B49" t="n">
-        <v>92682</v>
+        <v>80488</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5947,10 +5882,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>594612</v>
+        <v>594627</v>
       </c>
       <c r="R49" t="n">
-        <v>7106097</v>
+        <v>7106077</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5982,7 +5917,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5992,7 +5927,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6007,26 +5942,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Eriksson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134040809</v>
+        <v>134036147</v>
       </c>
       <c r="B50" t="n">
-        <v>91981</v>
+        <v>80488</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6034,37 +5965,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>594482</v>
+        <v>594500</v>
       </c>
       <c r="R50" t="n">
-        <v>7106066</v>
+        <v>7106009</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6093,7 +6024,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6103,7 +6034,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6118,12 +6049,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6134,10 +6065,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134041938</v>
+        <v>134036152</v>
       </c>
       <c r="B51" t="n">
-        <v>91963</v>
+        <v>80488</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6145,34 +6076,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>594721</v>
+        <v>594475</v>
       </c>
       <c r="R51" t="n">
-        <v>7106166</v>
+        <v>7106098</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6204,7 +6135,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6214,7 +6145,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6229,12 +6160,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6245,48 +6176,51 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134036158</v>
+        <v>134086724</v>
       </c>
       <c r="B52" t="n">
-        <v>98059</v>
+        <v>80488</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen A 2278-2026, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>594476</v>
+        <v>594543</v>
       </c>
       <c r="R52" t="n">
-        <v>7106135</v>
+        <v>7106175</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6315,7 +6249,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6325,7 +6259,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6334,18 +6273,19 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunnar Janson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Gunnar Janson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6356,45 +6296,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134036152</v>
+        <v>2072191</v>
       </c>
       <c r="B53" t="n">
-        <v>80481</v>
+        <v>80461</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>S Lomsjö, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>594475</v>
+        <v>594704</v>
       </c>
       <c r="R53" t="n">
-        <v>7106098</v>
+        <v>7106194</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6421,22 +6361,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2012-09-06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2012-09-06</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6451,64 +6381,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134036179</v>
+        <v>134004112</v>
       </c>
       <c r="B54" t="n">
-        <v>91967</v>
+        <v>80493</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>a 2278-2026, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>594582</v>
+        <v>594779</v>
       </c>
       <c r="R54" t="n">
-        <v>7106116</v>
+        <v>7106096</v>
       </c>
       <c r="S54" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6537,7 +6463,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6547,7 +6473,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6562,12 +6488,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6578,55 +6504,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134040817</v>
+        <v>134036163</v>
       </c>
       <c r="B55" t="n">
-        <v>79366</v>
+        <v>80493</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>594576</v>
+        <v>594604</v>
       </c>
       <c r="R55" t="n">
-        <v>7106159</v>
+        <v>7106104</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6655,7 +6574,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6665,7 +6584,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6674,19 +6593,18 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6697,10 +6615,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134036163</v>
+        <v>134041932</v>
       </c>
       <c r="B56" t="n">
-        <v>80486</v>
+        <v>80493</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6728,17 +6646,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>594604</v>
+        <v>594484</v>
       </c>
       <c r="R56" t="n">
-        <v>7106104</v>
+        <v>7106025</v>
       </c>
       <c r="S56" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6767,7 +6685,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6777,7 +6695,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6792,12 +6710,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6808,30 +6726,34 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134036175</v>
+        <v>134036165</v>
       </c>
       <c r="B57" t="n">
-        <v>91987</v>
+        <v>80500</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6839,13 +6761,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>594758</v>
+        <v>594602</v>
       </c>
       <c r="R57" t="n">
-        <v>7106168</v>
+        <v>7106101</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6874,7 +6796,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6884,7 +6806,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6915,32 +6837,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134040818</v>
+        <v>134040805</v>
       </c>
       <c r="B58" t="n">
-        <v>91963</v>
+        <v>80500</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6950,10 +6872,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>594598</v>
+        <v>594524</v>
       </c>
       <c r="R58" t="n">
-        <v>7106142</v>
+        <v>7106017</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6985,7 +6907,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6995,7 +6917,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7026,45 +6948,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134041937</v>
+        <v>134040808</v>
       </c>
       <c r="B59" t="n">
-        <v>91963</v>
+        <v>80500</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Åsele Söndag Inventering, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>594714</v>
+        <v>594483</v>
       </c>
       <c r="R59" t="n">
-        <v>7106130</v>
+        <v>7106035</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7096,7 +7018,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7106,7 +7028,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7121,12 +7043,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7137,48 +7059,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134036145</v>
+        <v>134040810</v>
       </c>
       <c r="B60" t="n">
-        <v>91967</v>
+        <v>80500</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>594513</v>
+        <v>594501</v>
       </c>
       <c r="R60" t="n">
-        <v>7106004</v>
+        <v>7106169</v>
       </c>
       <c r="S60" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7207,7 +7129,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7217,7 +7139,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7232,12 +7154,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7248,48 +7170,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134086724</v>
+        <v>134041933</v>
       </c>
       <c r="B61" t="n">
-        <v>80481</v>
+        <v>80500</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Fårkullen A 2278-2026, Ås lm</t>
+          <t>Åsele Söndag Inventering, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>594543</v>
+        <v>594496</v>
       </c>
       <c r="R61" t="n">
-        <v>7106175</v>
+        <v>7106047</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7321,7 +7240,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7331,12 +7250,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7345,19 +7259,18 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Gunnar Janson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Gunnar Janson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7368,48 +7281,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134040812</v>
+        <v>134036149</v>
       </c>
       <c r="B62" t="n">
-        <v>83356</v>
+        <v>57972</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1467</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Fårkullen, Ås lm</t>
+          <t>Fårkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>594508</v>
+        <v>594477</v>
       </c>
       <c r="R62" t="n">
-        <v>7106172</v>
+        <v>7106037</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7438,7 +7351,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7448,7 +7361,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7463,15 +7376,1500 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>134004110</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>a 2278-2026, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>594497</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7106185</v>
+      </c>
+      <c r="S63" t="n">
+        <v>8</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>134004118</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>a 2278-2026, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>594838</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7106118</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>osäker fynd</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>134004119</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>a 2278-2026, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>594745</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7106148</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>osäker fynd</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>134004122</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>a 2278-2026, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>594531</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7105963</v>
+      </c>
+      <c r="S66" t="n">
+        <v>8</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>osäker fynd</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>134036150</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>594479</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7106056</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>134004120</v>
+      </c>
+      <c r="B68" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>a 2278-2026, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>594671</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7106200</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>134036148</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>594489</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7106044</v>
+      </c>
+      <c r="S69" t="n">
+        <v>32</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>134036158</v>
+      </c>
+      <c r="B70" t="n">
+        <v>98066</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>594476</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7106135</v>
+      </c>
+      <c r="S70" t="n">
+        <v>6</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>134036173</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>594691</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7106160</v>
+      </c>
+      <c r="S71" t="n">
+        <v>63</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>134040821</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>594701</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7106149</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
           <t>Alva Danielsson</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
+      <c r="AX72" t="inlineStr">
         <is>
           <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
         </is>
       </c>
-      <c r="AY62" t="inlineStr">
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>134040822</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>594708</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7106124</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>134040831</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>594501</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7106065</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, David Häggblad, Karin Häggblad, Sture Gustafsson, Anton Brall, Gunnar Janson, Patrik Eriksson, Katerina Shytaj, Maria Persbo</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>134036155</v>
+      </c>
+      <c r="B75" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Fårkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>594466</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7106117</v>
+      </c>
+      <c r="S75" t="n">
+        <v>8</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Gunnar Janson, Katerina Shytaj, Anton Brall, Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
